--- a/research/traditional_assets/database/data/egypt/egypt_chemical_diversified.xlsx
+++ b/research/traditional_assets/database/data/egypt/egypt_chemical_diversified.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1677669351670166</v>
+        <v>0.1674243345628908</v>
       </c>
       <c r="C2">
-        <v>572.5974823869595</v>
+        <v>568.7583214660013</v>
       </c>
       <c r="D2">
-        <v>500.4974823869596</v>
+        <v>501.9073214660014</v>
       </c>
       <c r="E2">
-        <v>-248.2</v>
+        <v>-242.951</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>5.249</v>
       </c>
       <c r="G2">
         <v>72.09999999999999</v>
@@ -1445,28 +1445,28 @@
         <v>36.2</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.2640246999999999</v>
       </c>
       <c r="N2">
-        <v>36.2</v>
+        <v>35.9359753</v>
       </c>
       <c r="O2">
-        <v>8.145000000000001</v>
+        <v>8.085594442500001</v>
       </c>
       <c r="P2">
-        <v>28.055</v>
+        <v>27.8503808575</v>
       </c>
       <c r="Q2">
-        <v>41.455</v>
+        <v>41.2503808575</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1677669351670166</v>
+        <v>0.1687217268312028</v>
       </c>
       <c r="T2">
-        <v>0.8504074490426662</v>
+        <v>0.8570646790730506</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>137.1083841776925</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1674243345628908</v>
+        <v>0.167081733958765</v>
       </c>
       <c r="C3">
-        <v>568.7583214660013</v>
+        <v>564.9271256640175</v>
       </c>
       <c r="D3">
-        <v>501.9073214660014</v>
+        <v>503.3251256640175</v>
       </c>
       <c r="E3">
-        <v>-242.951</v>
+        <v>-237.702</v>
       </c>
       <c r="F3">
-        <v>5.249</v>
+        <v>10.498</v>
       </c>
       <c r="G3">
         <v>72.09999999999999</v>
@@ -1527,28 +1527,28 @@
         <v>36.2</v>
       </c>
       <c r="M3">
-        <v>0.2640246999999999</v>
+        <v>0.5280493999999999</v>
       </c>
       <c r="N3">
-        <v>35.9359753</v>
+        <v>35.6719506</v>
       </c>
       <c r="O3">
-        <v>8.085594442500001</v>
+        <v>8.026188885000002</v>
       </c>
       <c r="P3">
-        <v>27.8503808575</v>
+        <v>27.645761715</v>
       </c>
       <c r="Q3">
-        <v>41.2503808575</v>
+        <v>41.045761715</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1687217268312028</v>
+        <v>0.1696960040395561</v>
       </c>
       <c r="T3">
-        <v>0.8570646790730506</v>
+        <v>0.8638577709407899</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>137.1083841776925</v>
+        <v>68.55419208884625</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.167081733958765</v>
+        <v>0.1667391333546392</v>
       </c>
       <c r="C4">
-        <v>564.9271256640175</v>
+        <v>561.1039626726102</v>
       </c>
       <c r="D4">
-        <v>503.3251256640175</v>
+        <v>504.7509626726102</v>
       </c>
       <c r="E4">
-        <v>-237.702</v>
+        <v>-232.453</v>
       </c>
       <c r="F4">
-        <v>10.498</v>
+        <v>15.747</v>
       </c>
       <c r="G4">
         <v>72.09999999999999</v>
@@ -1609,28 +1609,28 @@
         <v>36.2</v>
       </c>
       <c r="M4">
-        <v>0.5280493999999999</v>
+        <v>0.7920740999999999</v>
       </c>
       <c r="N4">
-        <v>35.6719506</v>
+        <v>35.4079259</v>
       </c>
       <c r="O4">
-        <v>8.026188885000002</v>
+        <v>7.966783327500001</v>
       </c>
       <c r="P4">
-        <v>27.645761715</v>
+        <v>27.4411425725</v>
       </c>
       <c r="Q4">
-        <v>41.045761715</v>
+        <v>40.8411425725</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1696960040395561</v>
+        <v>0.1706903694377724</v>
       </c>
       <c r="T4">
-        <v>0.8638577709407899</v>
+        <v>0.8707909265583795</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>68.55419208884625</v>
+        <v>45.7027947258975</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1667391333546392</v>
+        <v>0.1663965327505134</v>
       </c>
       <c r="C5">
-        <v>561.1039626726102</v>
+        <v>557.2889009525976</v>
       </c>
       <c r="D5">
-        <v>504.7509626726102</v>
+        <v>506.1849009525976</v>
       </c>
       <c r="E5">
-        <v>-232.453</v>
+        <v>-227.204</v>
       </c>
       <c r="F5">
-        <v>15.747</v>
+        <v>20.996</v>
       </c>
       <c r="G5">
         <v>72.09999999999999</v>
@@ -1691,28 +1691,28 @@
         <v>36.2</v>
       </c>
       <c r="M5">
-        <v>0.7920740999999999</v>
+        <v>1.0560988</v>
       </c>
       <c r="N5">
-        <v>35.4079259</v>
+        <v>35.1439012</v>
       </c>
       <c r="O5">
-        <v>7.966783327500001</v>
+        <v>7.907377770000001</v>
       </c>
       <c r="P5">
-        <v>27.4411425725</v>
+        <v>27.23652343</v>
       </c>
       <c r="Q5">
-        <v>40.8411425725</v>
+        <v>40.63652343</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1706903694377724</v>
+        <v>0.1717054507817848</v>
       </c>
       <c r="T5">
-        <v>0.8707909265583795</v>
+        <v>0.8778685229180022</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>45.7027947258975</v>
+        <v>34.27709604442312</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1663965327505134</v>
+        <v>0.1660539321463876</v>
       </c>
       <c r="C6">
-        <v>557.2889009525976</v>
+        <v>553.4820097449705</v>
       </c>
       <c r="D6">
-        <v>506.1849009525976</v>
+        <v>507.6270097449705</v>
       </c>
       <c r="E6">
-        <v>-227.204</v>
+        <v>-221.955</v>
       </c>
       <c r="F6">
-        <v>20.996</v>
+        <v>26.245</v>
       </c>
       <c r="G6">
         <v>72.09999999999999</v>
@@ -1773,28 +1773,28 @@
         <v>36.2</v>
       </c>
       <c r="M6">
-        <v>1.0560988</v>
+        <v>1.3201235</v>
       </c>
       <c r="N6">
-        <v>35.1439012</v>
+        <v>34.8798765</v>
       </c>
       <c r="O6">
-        <v>7.907377770000001</v>
+        <v>7.8479722125</v>
       </c>
       <c r="P6">
-        <v>27.23652343</v>
+        <v>27.0319042875</v>
       </c>
       <c r="Q6">
-        <v>40.63652343</v>
+        <v>40.4319042875</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1717054507817848</v>
+        <v>0.1727419022593554</v>
       </c>
       <c r="T6">
-        <v>0.8778685229180022</v>
+        <v>0.8850951213062486</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>34.27709604442312</v>
+        <v>27.42167683553849</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1660539321463876</v>
+        <v>0.1657113315422618</v>
       </c>
       <c r="C7">
-        <v>553.4820097449705</v>
+        <v>549.6833590820379</v>
       </c>
       <c r="D7">
-        <v>507.6270097449705</v>
+        <v>509.0773590820379</v>
       </c>
       <c r="E7">
-        <v>-221.955</v>
+        <v>-216.706</v>
       </c>
       <c r="F7">
-        <v>26.245</v>
+        <v>31.494</v>
       </c>
       <c r="G7">
         <v>72.09999999999999</v>
@@ -1855,28 +1855,28 @@
         <v>36.2</v>
       </c>
       <c r="M7">
-        <v>1.3201235</v>
+        <v>1.5841482</v>
       </c>
       <c r="N7">
-        <v>34.8798765</v>
+        <v>34.6158518</v>
       </c>
       <c r="O7">
-        <v>7.8479722125</v>
+        <v>7.788566655</v>
       </c>
       <c r="P7">
-        <v>27.0319042875</v>
+        <v>26.827285145</v>
       </c>
       <c r="Q7">
-        <v>40.4319042875</v>
+        <v>40.227285145</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1727419022593554</v>
+        <v>0.1738004058960232</v>
       </c>
       <c r="T7">
-        <v>0.8850951213062486</v>
+        <v>0.8924754771070108</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>27.42167683553849</v>
+        <v>22.85139736294875</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1657113315422618</v>
+        <v>0.1653687309381361</v>
       </c>
       <c r="C8">
-        <v>549.6833590820379</v>
+        <v>545.8930197987638</v>
       </c>
       <c r="D8">
-        <v>509.0773590820379</v>
+        <v>510.5360197987639</v>
       </c>
       <c r="E8">
-        <v>-216.706</v>
+        <v>-211.457</v>
       </c>
       <c r="F8">
-        <v>31.494</v>
+        <v>36.74299999999999</v>
       </c>
       <c r="G8">
         <v>72.09999999999999</v>
@@ -1937,28 +1937,28 @@
         <v>36.2</v>
       </c>
       <c r="M8">
-        <v>1.5841482</v>
+        <v>1.8481729</v>
       </c>
       <c r="N8">
-        <v>34.6158518</v>
+        <v>34.3518271</v>
       </c>
       <c r="O8">
-        <v>7.788566655</v>
+        <v>7.7291610975</v>
       </c>
       <c r="P8">
-        <v>26.827285145</v>
+        <v>26.6226660025</v>
       </c>
       <c r="Q8">
-        <v>40.227285145</v>
+        <v>40.0226660025</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1738004058960232</v>
+        <v>0.1748816730517592</v>
       </c>
       <c r="T8">
-        <v>0.8924754771070108</v>
+        <v>0.9000145502368218</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>22.85139736294875</v>
+        <v>19.58691202538464</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1653687309381361</v>
+        <v>0.1650261303340103</v>
       </c>
       <c r="C9">
-        <v>545.893019798764</v>
+        <v>542.1110635443006</v>
       </c>
       <c r="D9">
-        <v>510.5360197987641</v>
+        <v>512.0030635443005</v>
       </c>
       <c r="E9">
-        <v>-211.457</v>
+        <v>-206.208</v>
       </c>
       <c r="F9">
-        <v>36.743</v>
+        <v>41.992</v>
       </c>
       <c r="G9">
         <v>72.09999999999999</v>
@@ -2019,28 +2019,28 @@
         <v>36.2</v>
       </c>
       <c r="M9">
-        <v>1.8481729</v>
+        <v>2.1121976</v>
       </c>
       <c r="N9">
-        <v>34.3518271</v>
+        <v>34.0878024</v>
       </c>
       <c r="O9">
-        <v>7.7291610975</v>
+        <v>7.669755540000001</v>
       </c>
       <c r="P9">
-        <v>26.6226660025</v>
+        <v>26.41804686</v>
       </c>
       <c r="Q9">
-        <v>40.0226660025</v>
+        <v>39.81804686</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1748816730517592</v>
+        <v>0.1759864460152286</v>
       </c>
       <c r="T9">
-        <v>0.9000145502368218</v>
+        <v>0.9077175162607588</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>19.58691202538464</v>
+        <v>17.13854802221156</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1650261303340103</v>
+        <v>0.1646835297298845</v>
       </c>
       <c r="C10">
-        <v>542.1110635443006</v>
+        <v>538.337562793718</v>
       </c>
       <c r="D10">
-        <v>512.0030635443005</v>
+        <v>513.478562793718</v>
       </c>
       <c r="E10">
-        <v>-206.208</v>
+        <v>-200.959</v>
       </c>
       <c r="F10">
-        <v>41.992</v>
+        <v>47.241</v>
       </c>
       <c r="G10">
         <v>72.09999999999999</v>
@@ -2101,28 +2101,28 @@
         <v>36.2</v>
       </c>
       <c r="M10">
-        <v>2.1121976</v>
+        <v>2.3762223</v>
       </c>
       <c r="N10">
-        <v>34.0878024</v>
+        <v>33.8237777</v>
       </c>
       <c r="O10">
-        <v>7.669755540000001</v>
+        <v>7.610349982500001</v>
       </c>
       <c r="P10">
-        <v>26.41804686</v>
+        <v>26.2134277175</v>
       </c>
       <c r="Q10">
-        <v>39.81804686</v>
+        <v>39.6134277175</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1759864460152286</v>
+        <v>0.1771154997031698</v>
       </c>
       <c r="T10">
-        <v>0.9077175162607588</v>
+        <v>0.9155897782412661</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>17.13854802221156</v>
+        <v>15.2342649086325</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1646835297298845</v>
+        <v>0.1643409291257587</v>
       </c>
       <c r="C11">
-        <v>538.337562793718</v>
+        <v>534.5725908599408</v>
       </c>
       <c r="D11">
-        <v>513.478562793718</v>
+        <v>514.9625908599407</v>
       </c>
       <c r="E11">
-        <v>-200.959</v>
+        <v>-195.71</v>
       </c>
       <c r="F11">
-        <v>47.241</v>
+        <v>52.48999999999999</v>
       </c>
       <c r="G11">
         <v>72.09999999999999</v>
@@ -2183,28 +2183,28 @@
         <v>36.2</v>
       </c>
       <c r="M11">
-        <v>2.3762223</v>
+        <v>2.640247</v>
       </c>
       <c r="N11">
-        <v>33.8237777</v>
+        <v>33.559753</v>
       </c>
       <c r="O11">
-        <v>7.610349982500001</v>
+        <v>7.550944425</v>
       </c>
       <c r="P11">
-        <v>26.2134277175</v>
+        <v>26.008808575</v>
       </c>
       <c r="Q11">
-        <v>39.6134277175</v>
+        <v>39.408808575</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1771154997031698</v>
+        <v>0.1782696434730652</v>
       </c>
       <c r="T11">
-        <v>0.9155897782412661</v>
+        <v>0.9236369793768957</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>15.2342649086325</v>
+        <v>13.71083841776925</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1643409291257587</v>
+        <v>0.1641262035216329</v>
       </c>
       <c r="C12">
-        <v>534.5725908599408</v>
+        <v>530.2580893068917</v>
       </c>
       <c r="D12">
-        <v>514.9625908599407</v>
+        <v>515.8970893068918</v>
       </c>
       <c r="E12">
-        <v>-195.71</v>
+        <v>-190.461</v>
       </c>
       <c r="F12">
-        <v>52.49</v>
+        <v>57.739</v>
       </c>
       <c r="G12">
         <v>72.09999999999999</v>
@@ -2265,45 +2265,45 @@
         <v>36.2</v>
       </c>
       <c r="M12">
-        <v>2.640247</v>
+        <v>2.9908802</v>
       </c>
       <c r="N12">
-        <v>33.559753</v>
+        <v>33.2091198</v>
       </c>
       <c r="O12">
-        <v>7.550944425</v>
+        <v>7.472051955000001</v>
       </c>
       <c r="P12">
-        <v>26.008808575</v>
+        <v>25.737067845</v>
       </c>
       <c r="Q12">
-        <v>39.408808575</v>
+        <v>39.137067845</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1782696434730652</v>
+        <v>0.1794497230580145</v>
       </c>
       <c r="T12">
-        <v>0.9236369793768957</v>
+        <v>0.9318650164931013</v>
       </c>
       <c r="U12">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V12">
         <v>0.225</v>
       </c>
       <c r="W12">
-        <v>0.0389825</v>
+        <v>0.040145</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y12">
-        <v>13.71083841776925</v>
+        <v>12.10346037932245</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1641262035216329</v>
+        <v>0.1637952279175071</v>
       </c>
       <c r="C13">
-        <v>530.2580893068917</v>
+        <v>526.4561762256906</v>
       </c>
       <c r="D13">
-        <v>515.8970893068918</v>
+        <v>517.3441762256905</v>
       </c>
       <c r="E13">
-        <v>-190.461</v>
+        <v>-185.212</v>
       </c>
       <c r="F13">
-        <v>57.739</v>
+        <v>62.98799999999999</v>
       </c>
       <c r="G13">
         <v>72.09999999999999</v>
@@ -2347,28 +2347,28 @@
         <v>36.2</v>
       </c>
       <c r="M13">
-        <v>2.9908802</v>
+        <v>3.2627784</v>
       </c>
       <c r="N13">
-        <v>33.2091198</v>
+        <v>32.9372216</v>
       </c>
       <c r="O13">
-        <v>7.472051955000001</v>
+        <v>7.410874860000001</v>
       </c>
       <c r="P13">
-        <v>25.737067845</v>
+        <v>25.52634674</v>
       </c>
       <c r="Q13">
-        <v>39.137067845</v>
+        <v>38.92634674</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1794497230580145</v>
+        <v>0.1806566226335309</v>
       </c>
       <c r="T13">
-        <v>0.9318650164931013</v>
+        <v>0.9402800544528571</v>
       </c>
       <c r="U13">
         <v>0.0518</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>12.10346037932245</v>
+        <v>11.09483868104558</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1637952279175071</v>
+        <v>0.1634642523133814</v>
       </c>
       <c r="C14">
-        <v>526.4561762256906</v>
+        <v>522.662404112672</v>
       </c>
       <c r="D14">
-        <v>517.3441762256905</v>
+        <v>518.7994041126719</v>
       </c>
       <c r="E14">
-        <v>-185.212</v>
+        <v>-179.963</v>
       </c>
       <c r="F14">
-        <v>62.98799999999999</v>
+        <v>68.23699999999999</v>
       </c>
       <c r="G14">
         <v>72.09999999999999</v>
@@ -2429,28 +2429,28 @@
         <v>36.2</v>
       </c>
       <c r="M14">
-        <v>3.2627784</v>
+        <v>3.5346766</v>
       </c>
       <c r="N14">
-        <v>32.9372216</v>
+        <v>32.66532340000001</v>
       </c>
       <c r="O14">
-        <v>7.410874860000001</v>
+        <v>7.349697765000001</v>
       </c>
       <c r="P14">
-        <v>25.52634674</v>
+        <v>25.315625635</v>
       </c>
       <c r="Q14">
-        <v>38.92634674</v>
+        <v>38.715625635</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1806566226335309</v>
+        <v>0.1818912670268751</v>
       </c>
       <c r="T14">
-        <v>0.9402800544528571</v>
+        <v>0.9488885415611129</v>
       </c>
       <c r="U14">
         <v>0.0518</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>11.09483868104558</v>
+        <v>10.24138955173438</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1634642523133814</v>
+        <v>0.1633177267092555</v>
       </c>
       <c r="C15">
-        <v>522.662404112672</v>
+        <v>518.0602630865168</v>
       </c>
       <c r="D15">
-        <v>518.7994041126719</v>
+        <v>519.4462630865168</v>
       </c>
       <c r="E15">
-        <v>-179.963</v>
+        <v>-174.714</v>
       </c>
       <c r="F15">
-        <v>68.23699999999999</v>
+        <v>73.486</v>
       </c>
       <c r="G15">
         <v>72.09999999999999</v>
@@ -2511,45 +2511,45 @@
         <v>36.2</v>
       </c>
       <c r="M15">
-        <v>3.5346766</v>
+        <v>3.931501</v>
       </c>
       <c r="N15">
-        <v>32.66532340000001</v>
+        <v>32.26849900000001</v>
       </c>
       <c r="O15">
-        <v>7.349697765000001</v>
+        <v>7.260412275000001</v>
       </c>
       <c r="P15">
-        <v>25.315625635</v>
+        <v>25.00808672500001</v>
       </c>
       <c r="Q15">
-        <v>38.715625635</v>
+        <v>38.408086725</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1818912670268751</v>
+        <v>0.1831546240805297</v>
       </c>
       <c r="T15">
-        <v>0.9488885415611129</v>
+        <v>0.9576972260439792</v>
       </c>
       <c r="U15">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V15">
         <v>0.225</v>
       </c>
       <c r="W15">
-        <v>0.040145</v>
+        <v>0.0414625</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y15">
-        <v>10.24138955173438</v>
+        <v>9.207679204456518</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1633177267092555</v>
+        <v>0.1629999261051298</v>
       </c>
       <c r="C16">
-        <v>518.0602630865168</v>
+        <v>514.2197992665796</v>
       </c>
       <c r="D16">
-        <v>519.4462630865168</v>
+        <v>520.8547992665796</v>
       </c>
       <c r="E16">
-        <v>-174.714</v>
+        <v>-169.465</v>
       </c>
       <c r="F16">
-        <v>73.486</v>
+        <v>78.73500000000001</v>
       </c>
       <c r="G16">
         <v>72.09999999999999</v>
@@ -2593,28 +2593,28 @@
         <v>36.2</v>
       </c>
       <c r="M16">
-        <v>3.931501</v>
+        <v>4.212322500000001</v>
       </c>
       <c r="N16">
-        <v>32.26849900000001</v>
+        <v>31.9876775</v>
       </c>
       <c r="O16">
-        <v>7.260412275000001</v>
+        <v>7.197227437500001</v>
       </c>
       <c r="P16">
-        <v>25.00808672500001</v>
+        <v>24.7904500625</v>
       </c>
       <c r="Q16">
-        <v>38.408086725</v>
+        <v>38.19045006250001</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1831546240805297</v>
+        <v>0.1844477071825056</v>
       </c>
       <c r="T16">
-        <v>0.9576972260439792</v>
+        <v>0.9667131736911484</v>
       </c>
       <c r="U16">
         <v>0.0535</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>9.207679204456518</v>
+        <v>8.593833924159416</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1629999261051298</v>
+        <v>0.162682125501004</v>
       </c>
       <c r="C17">
-        <v>514.2197992665796</v>
+        <v>510.3869950207141</v>
       </c>
       <c r="D17">
-        <v>520.8547992665796</v>
+        <v>522.2709950207141</v>
       </c>
       <c r="E17">
-        <v>-169.465</v>
+        <v>-164.216</v>
       </c>
       <c r="F17">
-        <v>78.735</v>
+        <v>83.98399999999999</v>
       </c>
       <c r="G17">
         <v>72.09999999999999</v>
@@ -2675,28 +2675,28 @@
         <v>36.2</v>
       </c>
       <c r="M17">
-        <v>4.2123225</v>
+        <v>4.493144</v>
       </c>
       <c r="N17">
-        <v>31.9876775</v>
+        <v>31.706856</v>
       </c>
       <c r="O17">
-        <v>7.197227437500001</v>
+        <v>7.134042600000001</v>
       </c>
       <c r="P17">
-        <v>24.7904500625</v>
+        <v>24.5728134</v>
       </c>
       <c r="Q17">
-        <v>38.19045006250001</v>
+        <v>37.9728134</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1844477071825056</v>
+        <v>0.1857715779773857</v>
       </c>
       <c r="T17">
-        <v>0.9667131736911484</v>
+        <v>0.9759437867584883</v>
       </c>
       <c r="U17">
         <v>0.0535</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>8.593833924159416</v>
+        <v>8.056719303899452</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.162682125501004</v>
+        <v>0.1624697248968782</v>
       </c>
       <c r="C18">
-        <v>510.3869950207141</v>
+        <v>506.0888044527053</v>
       </c>
       <c r="D18">
-        <v>522.2709950207141</v>
+        <v>523.2218044527053</v>
       </c>
       <c r="E18">
-        <v>-164.216</v>
+        <v>-158.967</v>
       </c>
       <c r="F18">
-        <v>83.98399999999999</v>
+        <v>89.233</v>
       </c>
       <c r="G18">
         <v>72.09999999999999</v>
@@ -2757,45 +2757,45 @@
         <v>36.2</v>
       </c>
       <c r="M18">
-        <v>4.493144</v>
+        <v>4.845351900000001</v>
       </c>
       <c r="N18">
-        <v>31.706856</v>
+        <v>31.3546481</v>
       </c>
       <c r="O18">
-        <v>7.134042600000001</v>
+        <v>7.054795822500001</v>
       </c>
       <c r="P18">
-        <v>24.5728134</v>
+        <v>24.2998522775</v>
       </c>
       <c r="Q18">
-        <v>37.9728134</v>
+        <v>37.6998522775</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1857715779773857</v>
+        <v>0.1871273492733472</v>
       </c>
       <c r="T18">
-        <v>0.9759437867584883</v>
+        <v>0.9853968242370893</v>
       </c>
       <c r="U18">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V18">
         <v>0.225</v>
       </c>
       <c r="W18">
-        <v>0.0414625</v>
+        <v>0.0420825</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y18">
-        <v>8.056719303899452</v>
+        <v>7.47107759087632</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1624697248968782</v>
+        <v>0.1621581242927524</v>
       </c>
       <c r="C19">
-        <v>506.0888044527053</v>
+        <v>502.2409634293579</v>
       </c>
       <c r="D19">
-        <v>523.2218044527053</v>
+        <v>524.6229634293579</v>
       </c>
       <c r="E19">
-        <v>-158.967</v>
+        <v>-153.718</v>
       </c>
       <c r="F19">
-        <v>89.233</v>
+        <v>94.48200000000001</v>
       </c>
       <c r="G19">
         <v>72.09999999999999</v>
@@ -2839,28 +2839,28 @@
         <v>36.2</v>
       </c>
       <c r="M19">
-        <v>4.845351900000001</v>
+        <v>5.130372600000001</v>
       </c>
       <c r="N19">
-        <v>31.3546481</v>
+        <v>31.0696274</v>
       </c>
       <c r="O19">
-        <v>7.054795822500001</v>
+        <v>6.990666165</v>
       </c>
       <c r="P19">
-        <v>24.2998522775</v>
+        <v>24.078961235</v>
       </c>
       <c r="Q19">
-        <v>37.6998522775</v>
+        <v>37.478961235</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1871273492733472</v>
+        <v>0.1885161881618932</v>
       </c>
       <c r="T19">
-        <v>0.9853968242370893</v>
+        <v>0.9950804236054125</v>
       </c>
       <c r="U19">
         <v>0.0543</v>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>7.47107759087632</v>
+        <v>7.056017724716523</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1621581242927524</v>
+        <v>0.1618465236886266</v>
       </c>
       <c r="C20">
-        <v>502.2409634293579</v>
+        <v>498.4006470085529</v>
       </c>
       <c r="D20">
-        <v>524.6229634293578</v>
+        <v>526.0316470085529</v>
       </c>
       <c r="E20">
-        <v>-153.718</v>
+        <v>-148.469</v>
       </c>
       <c r="F20">
-        <v>94.482</v>
+        <v>99.73099999999999</v>
       </c>
       <c r="G20">
         <v>72.09999999999999</v>
@@ -2921,28 +2921,28 @@
         <v>36.2</v>
       </c>
       <c r="M20">
-        <v>5.1303726</v>
+        <v>5.4153933</v>
       </c>
       <c r="N20">
-        <v>31.0696274</v>
+        <v>30.7846067</v>
       </c>
       <c r="O20">
-        <v>6.990666165</v>
+        <v>6.926536507500002</v>
       </c>
       <c r="P20">
-        <v>24.078961235</v>
+        <v>23.8580701925</v>
       </c>
       <c r="Q20">
-        <v>37.478961235</v>
+        <v>37.2580701925</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1885161881618932</v>
+        <v>0.1899393193686748</v>
       </c>
       <c r="T20">
-        <v>0.9950804236054125</v>
+        <v>1.005003124192706</v>
       </c>
       <c r="U20">
         <v>0.0543</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>7.056017724716525</v>
+        <v>6.684648370784076</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1618465236886266</v>
+        <v>0.1615349230845008</v>
       </c>
       <c r="C21">
-        <v>498.4006470085529</v>
+        <v>494.5679159672101</v>
       </c>
       <c r="D21">
-        <v>526.0316470085529</v>
+        <v>527.4479159672101</v>
       </c>
       <c r="E21">
-        <v>-148.469</v>
+        <v>-143.22</v>
       </c>
       <c r="F21">
-        <v>99.73099999999999</v>
+        <v>104.98</v>
       </c>
       <c r="G21">
         <v>72.09999999999999</v>
@@ -3003,28 +3003,28 @@
         <v>36.2</v>
       </c>
       <c r="M21">
-        <v>5.4153933</v>
+        <v>5.700414</v>
       </c>
       <c r="N21">
-        <v>30.7846067</v>
+        <v>30.499586</v>
       </c>
       <c r="O21">
-        <v>6.926536507500002</v>
+        <v>6.86240685</v>
       </c>
       <c r="P21">
-        <v>23.8580701925</v>
+        <v>23.63717915</v>
       </c>
       <c r="Q21">
-        <v>37.2580701925</v>
+        <v>37.03717915</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1899393193686748</v>
+        <v>0.1913980288556261</v>
       </c>
       <c r="T21">
-        <v>1.005003124192706</v>
+        <v>1.015173892294683</v>
       </c>
       <c r="U21">
         <v>0.0543</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>6.684648370784076</v>
+        <v>6.350415952244872</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1615349230845008</v>
+        <v>0.161386072480375</v>
       </c>
       <c r="C22">
-        <v>494.5679159672101</v>
+        <v>489.9981581912243</v>
       </c>
       <c r="D22">
-        <v>527.4479159672101</v>
+        <v>528.1271581912242</v>
       </c>
       <c r="E22">
-        <v>-143.22</v>
+        <v>-137.971</v>
       </c>
       <c r="F22">
-        <v>104.98</v>
+        <v>110.229</v>
       </c>
       <c r="G22">
         <v>72.09999999999999</v>
@@ -3085,45 +3085,45 @@
         <v>36.2</v>
       </c>
       <c r="M22">
-        <v>5.700414</v>
+        <v>6.0956637</v>
       </c>
       <c r="N22">
-        <v>30.499586</v>
+        <v>30.1043363</v>
       </c>
       <c r="O22">
-        <v>6.86240685</v>
+        <v>6.773475667500001</v>
       </c>
       <c r="P22">
-        <v>23.63717915</v>
+        <v>23.3308606325</v>
       </c>
       <c r="Q22">
-        <v>37.03717915</v>
+        <v>36.7308606325</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1913980288556261</v>
+        <v>0.1928936676966773</v>
       </c>
       <c r="T22">
-        <v>1.015173892294683</v>
+        <v>1.025602148196709</v>
       </c>
       <c r="U22">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V22">
         <v>0.225</v>
       </c>
       <c r="W22">
-        <v>0.0420825</v>
+        <v>0.0428575</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y22">
-        <v>6.350415952244872</v>
+        <v>5.938647829275753</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.161386072480375</v>
+        <v>0.1610822218762493</v>
       </c>
       <c r="C23">
-        <v>489.9981581912243</v>
+        <v>486.1411486773537</v>
       </c>
       <c r="D23">
-        <v>528.1271581912242</v>
+        <v>529.5191486773537</v>
       </c>
       <c r="E23">
-        <v>-137.971</v>
+        <v>-132.722</v>
       </c>
       <c r="F23">
-        <v>110.229</v>
+        <v>115.478</v>
       </c>
       <c r="G23">
         <v>72.09999999999999</v>
@@ -3167,28 +3167,28 @@
         <v>36.2</v>
       </c>
       <c r="M23">
-        <v>6.095663699999999</v>
+        <v>6.3859334</v>
       </c>
       <c r="N23">
-        <v>30.1043363</v>
+        <v>29.8140666</v>
       </c>
       <c r="O23">
-        <v>6.773475667500001</v>
+        <v>6.708164985000001</v>
       </c>
       <c r="P23">
-        <v>23.3308606325</v>
+        <v>23.105901615</v>
       </c>
       <c r="Q23">
-        <v>36.7308606325</v>
+        <v>36.50590161500001</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1928936676966773</v>
+        <v>0.1944276562516016</v>
       </c>
       <c r="T23">
-        <v>1.025602148196709</v>
+        <v>1.036297795275711</v>
       </c>
       <c r="U23">
         <v>0.0553</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>5.938647829275753</v>
+        <v>5.668709291581401</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1610822218762493</v>
+        <v>0.1607783712721235</v>
       </c>
       <c r="C24">
-        <v>486.1411486773537</v>
+        <v>482.2914963237124</v>
       </c>
       <c r="D24">
-        <v>529.5191486773537</v>
+        <v>530.9184963237124</v>
       </c>
       <c r="E24">
-        <v>-132.722</v>
+        <v>-127.473</v>
       </c>
       <c r="F24">
-        <v>115.478</v>
+        <v>120.727</v>
       </c>
       <c r="G24">
         <v>72.09999999999999</v>
@@ -3249,28 +3249,28 @@
         <v>36.2</v>
       </c>
       <c r="M24">
-        <v>6.3859334</v>
+        <v>6.6762031</v>
       </c>
       <c r="N24">
-        <v>29.8140666</v>
+        <v>29.5237969</v>
       </c>
       <c r="O24">
-        <v>6.708164985000001</v>
+        <v>6.6428543025</v>
       </c>
       <c r="P24">
-        <v>23.105901615</v>
+        <v>22.8809425975</v>
       </c>
       <c r="Q24">
-        <v>36.50590161500001</v>
+        <v>36.2809425975</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1944276562516016</v>
+        <v>0.1960014886650954</v>
       </c>
       <c r="T24">
-        <v>1.036297795275711</v>
+        <v>1.047271251369751</v>
       </c>
       <c r="U24">
         <v>0.0553</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>5.668709291581401</v>
+        <v>5.422243670208295</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1607783712721235</v>
+        <v>0.1604745206679977</v>
       </c>
       <c r="C25">
-        <v>482.2914963237124</v>
+        <v>478.4492596126261</v>
       </c>
       <c r="D25">
-        <v>530.9184963237124</v>
+        <v>532.325259612626</v>
       </c>
       <c r="E25">
-        <v>-127.473</v>
+        <v>-122.224</v>
       </c>
       <c r="F25">
-        <v>120.727</v>
+        <v>125.976</v>
       </c>
       <c r="G25">
         <v>72.09999999999999</v>
@@ -3331,28 +3331,28 @@
         <v>36.2</v>
       </c>
       <c r="M25">
-        <v>6.6762031</v>
+        <v>6.9664728</v>
       </c>
       <c r="N25">
-        <v>29.5237969</v>
+        <v>29.2335272</v>
       </c>
       <c r="O25">
-        <v>6.6428543025</v>
+        <v>6.577543620000001</v>
       </c>
       <c r="P25">
-        <v>22.8809425975</v>
+        <v>22.65598358</v>
       </c>
       <c r="Q25">
-        <v>36.2809425975</v>
+        <v>36.05598358</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1960014886650954</v>
+        <v>0.1976167377210496</v>
       </c>
       <c r="T25">
-        <v>1.047271251369751</v>
+        <v>1.058533482624161</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.422243670208295</v>
+        <v>5.196316850616284</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1604745206679977</v>
+        <v>0.1601706700638719</v>
       </c>
       <c r="C26">
-        <v>478.4492596126261</v>
+        <v>474.6144976479054</v>
       </c>
       <c r="D26">
-        <v>532.325259612626</v>
+        <v>533.7394976479054</v>
       </c>
       <c r="E26">
-        <v>-122.224</v>
+        <v>-116.975</v>
       </c>
       <c r="F26">
-        <v>125.976</v>
+        <v>131.225</v>
       </c>
       <c r="G26">
         <v>72.09999999999999</v>
@@ -3413,28 +3413,28 @@
         <v>36.2</v>
       </c>
       <c r="M26">
-        <v>6.966472799999999</v>
+        <v>7.2567425</v>
       </c>
       <c r="N26">
-        <v>29.2335272</v>
+        <v>28.9432575</v>
       </c>
       <c r="O26">
-        <v>6.577543620000001</v>
+        <v>6.5122329375</v>
       </c>
       <c r="P26">
-        <v>22.65598358</v>
+        <v>22.4310245625</v>
       </c>
       <c r="Q26">
-        <v>36.05598358</v>
+        <v>35.8310245625</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1976167377210496</v>
+        <v>0.1992750600851625</v>
       </c>
       <c r="T26">
-        <v>1.058533482624161</v>
+        <v>1.070096040045355</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.196316850616284</v>
+        <v>4.988464176591632</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1601706700638719</v>
+        <v>0.1598668194597461</v>
       </c>
       <c r="C27">
-        <v>474.6144976479054</v>
+        <v>470.7872701631226</v>
       </c>
       <c r="D27">
-        <v>533.7394976479054</v>
+        <v>535.1612701631226</v>
       </c>
       <c r="E27">
-        <v>-116.975</v>
+        <v>-111.726</v>
       </c>
       <c r="F27">
-        <v>131.225</v>
+        <v>136.474</v>
       </c>
       <c r="G27">
         <v>72.09999999999999</v>
@@ -3495,28 +3495,28 @@
         <v>36.2</v>
       </c>
       <c r="M27">
-        <v>7.2567425</v>
+        <v>7.547012199999999</v>
       </c>
       <c r="N27">
-        <v>28.9432575</v>
+        <v>28.65298780000001</v>
       </c>
       <c r="O27">
-        <v>6.5122329375</v>
+        <v>6.446922255000001</v>
       </c>
       <c r="P27">
-        <v>22.4310245625</v>
+        <v>22.206065545</v>
       </c>
       <c r="Q27">
-        <v>35.8310245625</v>
+        <v>35.60606554500001</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1992750600851625</v>
+        <v>0.2009782019726299</v>
       </c>
       <c r="T27">
-        <v>1.070096040045355</v>
+        <v>1.081971099018473</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>4.988464176591632</v>
+        <v>4.796600169799647</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1598668194597461</v>
+        <v>0.1595629688556203</v>
       </c>
       <c r="C28">
-        <v>470.7872701631226</v>
+        <v>466.9676375300218</v>
       </c>
       <c r="D28">
-        <v>535.1612701631226</v>
+        <v>536.5906375300218</v>
       </c>
       <c r="E28">
-        <v>-111.726</v>
+        <v>-106.477</v>
       </c>
       <c r="F28">
-        <v>136.474</v>
+        <v>141.723</v>
       </c>
       <c r="G28">
         <v>72.09999999999999</v>
@@ -3577,28 +3577,28 @@
         <v>36.2</v>
       </c>
       <c r="M28">
-        <v>7.547012199999999</v>
+        <v>7.837281900000001</v>
       </c>
       <c r="N28">
-        <v>28.65298780000001</v>
+        <v>28.3627181</v>
       </c>
       <c r="O28">
-        <v>6.446922255000001</v>
+        <v>6.381611572500001</v>
       </c>
       <c r="P28">
-        <v>22.206065545</v>
+        <v>21.9811065275</v>
       </c>
       <c r="Q28">
-        <v>35.60606554500001</v>
+        <v>35.3811065275</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.2009782019726299</v>
+        <v>0.2027280052816717</v>
       </c>
       <c r="T28">
-        <v>1.081971099018473</v>
+        <v>1.094171502073047</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>4.796600169799647</v>
+        <v>4.618948311658919</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1595629688556203</v>
+        <v>0.1598016182514945</v>
       </c>
       <c r="C29">
-        <v>466.9676375300218</v>
+        <v>460.595346181685</v>
       </c>
       <c r="D29">
-        <v>536.5906375300218</v>
+        <v>535.467346181685</v>
       </c>
       <c r="E29">
-        <v>-106.477</v>
+        <v>-101.228</v>
       </c>
       <c r="F29">
-        <v>141.723</v>
+        <v>146.972</v>
       </c>
       <c r="G29">
         <v>72.09999999999999</v>
@@ -3659,45 +3659,45 @@
         <v>36.2</v>
       </c>
       <c r="M29">
-        <v>7.837281900000001</v>
+        <v>8.494981600000001</v>
       </c>
       <c r="N29">
-        <v>28.3627181</v>
+        <v>27.7050184</v>
       </c>
       <c r="O29">
-        <v>6.381611572500001</v>
+        <v>6.233629140000001</v>
       </c>
       <c r="P29">
-        <v>21.9811065275</v>
+        <v>21.47138926</v>
       </c>
       <c r="Q29">
-        <v>35.3811065275</v>
+        <v>34.87138926</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.2027280052816717</v>
+        <v>0.2045264142381868</v>
       </c>
       <c r="T29">
-        <v>1.094171502073047</v>
+        <v>1.10671080521247</v>
       </c>
       <c r="U29">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V29">
         <v>0.225</v>
       </c>
       <c r="W29">
-        <v>0.0428575</v>
+        <v>0.044795</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y29">
-        <v>4.618948311658919</v>
+        <v>4.261339424207817</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1598016182514945</v>
+        <v>0.1595171426473687</v>
       </c>
       <c r="C30">
-        <v>460.595346181685</v>
+        <v>456.685875062278</v>
       </c>
       <c r="D30">
-        <v>535.467346181685</v>
+        <v>536.806875062278</v>
       </c>
       <c r="E30">
-        <v>-101.228</v>
+        <v>-95.97899999999998</v>
       </c>
       <c r="F30">
-        <v>146.972</v>
+        <v>152.221</v>
       </c>
       <c r="G30">
         <v>72.09999999999999</v>
@@ -3741,28 +3741,28 @@
         <v>36.2</v>
       </c>
       <c r="M30">
-        <v>8.494981600000001</v>
+        <v>8.7983738</v>
       </c>
       <c r="N30">
-        <v>27.7050184</v>
+        <v>27.4016262</v>
       </c>
       <c r="O30">
-        <v>6.233629140000001</v>
+        <v>6.165365895000001</v>
       </c>
       <c r="P30">
-        <v>21.47138926</v>
+        <v>21.236260305</v>
       </c>
       <c r="Q30">
-        <v>34.87138926</v>
+        <v>34.636260305</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.2045264142381868</v>
+        <v>0.2063754826019278</v>
       </c>
       <c r="T30">
-        <v>1.10671080521247</v>
+        <v>1.119603328158637</v>
       </c>
       <c r="U30">
         <v>0.0578</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>4.261339424207817</v>
+        <v>4.11439668544203</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1595171426473687</v>
+        <v>0.160046417043243</v>
       </c>
       <c r="C31">
-        <v>456.685875062278</v>
+        <v>448.9499862665255</v>
       </c>
       <c r="D31">
-        <v>536.806875062278</v>
+        <v>534.3199862665255</v>
       </c>
       <c r="E31">
-        <v>-95.97900000000001</v>
+        <v>-90.72999999999999</v>
       </c>
       <c r="F31">
-        <v>152.221</v>
+        <v>157.47</v>
       </c>
       <c r="G31">
         <v>72.09999999999999</v>
@@ -3823,45 +3823,45 @@
         <v>36.2</v>
       </c>
       <c r="M31">
-        <v>8.798373799999998</v>
+        <v>9.652911</v>
       </c>
       <c r="N31">
-        <v>27.4016262</v>
+        <v>26.547089</v>
       </c>
       <c r="O31">
-        <v>6.165365895000001</v>
+        <v>5.973095025000001</v>
       </c>
       <c r="P31">
-        <v>21.236260305</v>
+        <v>20.573993975</v>
       </c>
       <c r="Q31">
-        <v>34.636260305</v>
+        <v>33.973993975</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.2063754826019278</v>
+        <v>0.2082773814903471</v>
       </c>
       <c r="T31">
-        <v>1.119603328158637</v>
+        <v>1.132864208903266</v>
       </c>
       <c r="U31">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V31">
         <v>0.225</v>
       </c>
       <c r="W31">
-        <v>0.044795</v>
+        <v>0.0475075</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y31">
-        <v>4.114396685442031</v>
+        <v>3.750164069678049</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.160046417043243</v>
+        <v>0.1597890664391172</v>
       </c>
       <c r="C32">
-        <v>448.9499862665255</v>
+        <v>444.9073087284751</v>
       </c>
       <c r="D32">
-        <v>534.3199862665255</v>
+        <v>535.5263087284751</v>
       </c>
       <c r="E32">
-        <v>-90.72999999999999</v>
+        <v>-85.48099999999999</v>
       </c>
       <c r="F32">
-        <v>157.47</v>
+        <v>162.719</v>
       </c>
       <c r="G32">
         <v>72.09999999999999</v>
@@ -3905,28 +3905,28 @@
         <v>36.2</v>
       </c>
       <c r="M32">
-        <v>9.652911</v>
+        <v>9.9746747</v>
       </c>
       <c r="N32">
-        <v>26.547089</v>
+        <v>26.2253253</v>
       </c>
       <c r="O32">
-        <v>5.973095025000001</v>
+        <v>5.9006981925</v>
       </c>
       <c r="P32">
-        <v>20.573993975</v>
+        <v>20.3246271075</v>
       </c>
       <c r="Q32">
-        <v>33.973993975</v>
+        <v>33.7246271075</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.2082773814903471</v>
+        <v>0.2102344078827785</v>
       </c>
       <c r="T32">
-        <v>1.132864208903266</v>
+        <v>1.146509463002812</v>
       </c>
       <c r="U32">
         <v>0.0613</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>3.750164069678049</v>
+        <v>3.629191035172305</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1597890664391172</v>
+        <v>0.1595317158349914</v>
       </c>
       <c r="C33">
-        <v>444.9073087284751</v>
+        <v>440.8700904910619</v>
       </c>
       <c r="D33">
-        <v>535.5263087284751</v>
+        <v>536.7380904910618</v>
       </c>
       <c r="E33">
-        <v>-85.48099999999999</v>
+        <v>-80.232</v>
       </c>
       <c r="F33">
-        <v>162.719</v>
+        <v>167.968</v>
       </c>
       <c r="G33">
         <v>72.09999999999999</v>
@@ -3987,28 +3987,28 @@
         <v>36.2</v>
       </c>
       <c r="M33">
-        <v>9.9746747</v>
+        <v>10.2964384</v>
       </c>
       <c r="N33">
-        <v>26.2253253</v>
+        <v>25.9035616</v>
       </c>
       <c r="O33">
-        <v>5.9006981925</v>
+        <v>5.828301360000001</v>
       </c>
       <c r="P33">
-        <v>20.3246271075</v>
+        <v>20.07526024</v>
       </c>
       <c r="Q33">
-        <v>33.7246271075</v>
+        <v>33.47526024</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.2102344078827785</v>
+        <v>0.2122489938749873</v>
       </c>
       <c r="T33">
-        <v>1.146509463002812</v>
+        <v>1.160556048105286</v>
       </c>
       <c r="U33">
         <v>0.0613</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>3.629191035172305</v>
+        <v>3.515778815323171</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1595317158349914</v>
+        <v>0.1599904652308656</v>
       </c>
       <c r="C34">
-        <v>440.8700904910619</v>
+        <v>433.4647959680677</v>
       </c>
       <c r="D34">
-        <v>536.7380904910618</v>
+        <v>534.5817959680677</v>
       </c>
       <c r="E34">
-        <v>-80.232</v>
+        <v>-74.98299999999998</v>
       </c>
       <c r="F34">
-        <v>167.968</v>
+        <v>173.217</v>
       </c>
       <c r="G34">
         <v>72.09999999999999</v>
@@ -4069,45 +4069,45 @@
         <v>36.2</v>
       </c>
       <c r="M34">
-        <v>10.2964384</v>
+        <v>11.1032097</v>
       </c>
       <c r="N34">
-        <v>25.9035616</v>
+        <v>25.0967903</v>
       </c>
       <c r="O34">
-        <v>5.828301360000001</v>
+        <v>5.6467778175</v>
       </c>
       <c r="P34">
-        <v>20.07526024</v>
+        <v>19.4500124825</v>
       </c>
       <c r="Q34">
-        <v>33.47526024</v>
+        <v>32.8500124825</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.2122489938749873</v>
+        <v>0.214323716762486</v>
       </c>
       <c r="T34">
-        <v>1.160556048105286</v>
+        <v>1.175021934255595</v>
       </c>
       <c r="U34">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V34">
         <v>0.225</v>
       </c>
       <c r="W34">
-        <v>0.0475075</v>
+        <v>0.04967750000000001</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y34">
-        <v>3.515778815323171</v>
+        <v>3.260318500514315</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1599904652308656</v>
+        <v>0.1597548146267398</v>
       </c>
       <c r="C35">
-        <v>433.4647959680677</v>
+        <v>429.3212738154687</v>
       </c>
       <c r="D35">
-        <v>534.5817959680677</v>
+        <v>535.6872738154686</v>
       </c>
       <c r="E35">
-        <v>-74.98299999999998</v>
+        <v>-69.73399999999998</v>
       </c>
       <c r="F35">
-        <v>173.217</v>
+        <v>178.466</v>
       </c>
       <c r="G35">
         <v>72.09999999999999</v>
@@ -4151,28 +4151,28 @@
         <v>36.2</v>
       </c>
       <c r="M35">
-        <v>11.1032097</v>
+        <v>11.4396706</v>
       </c>
       <c r="N35">
-        <v>25.0967903</v>
+        <v>24.7603294</v>
       </c>
       <c r="O35">
-        <v>5.6467778175</v>
+        <v>5.571074115000001</v>
       </c>
       <c r="P35">
-        <v>19.4500124825</v>
+        <v>19.189255285</v>
       </c>
       <c r="Q35">
-        <v>32.8500124825</v>
+        <v>32.589255285</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.214323716762486</v>
+        <v>0.2164613100405149</v>
       </c>
       <c r="T35">
-        <v>1.175021934255595</v>
+        <v>1.189926180592276</v>
       </c>
       <c r="U35">
         <v>0.0641</v>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.260318500514315</v>
+        <v>3.164426779910953</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1597548146267398</v>
+        <v>0.159519164022614</v>
       </c>
       <c r="C36">
-        <v>429.3212738154687</v>
+        <v>425.1823332393315</v>
       </c>
       <c r="D36">
-        <v>535.6872738154686</v>
+        <v>536.7973332393315</v>
       </c>
       <c r="E36">
-        <v>-69.73399999999998</v>
+        <v>-64.48499999999999</v>
       </c>
       <c r="F36">
-        <v>178.466</v>
+        <v>183.715</v>
       </c>
       <c r="G36">
         <v>72.09999999999999</v>
@@ -4233,28 +4233,28 @@
         <v>36.2</v>
       </c>
       <c r="M36">
-        <v>11.4396706</v>
+        <v>11.7761315</v>
       </c>
       <c r="N36">
-        <v>24.7603294</v>
+        <v>24.4238685</v>
       </c>
       <c r="O36">
-        <v>5.571074115000001</v>
+        <v>5.495370412500001</v>
       </c>
       <c r="P36">
-        <v>19.189255285</v>
+        <v>18.9284980875</v>
       </c>
       <c r="Q36">
-        <v>32.589255285</v>
+        <v>32.3284980875</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.2164613100405149</v>
+        <v>0.2186646754194062</v>
       </c>
       <c r="T36">
-        <v>1.189926180592276</v>
+        <v>1.205289019123933</v>
       </c>
       <c r="U36">
         <v>0.0641</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.164426779910953</v>
+        <v>3.074014586199211</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.159519164022614</v>
+        <v>0.1614597134184882</v>
       </c>
       <c r="C37">
-        <v>425.1823332393315</v>
+        <v>410.9268978096035</v>
       </c>
       <c r="D37">
-        <v>536.7973332393315</v>
+        <v>527.7908978096035</v>
       </c>
       <c r="E37">
-        <v>-64.48499999999999</v>
+        <v>-59.23599999999996</v>
       </c>
       <c r="F37">
-        <v>183.715</v>
+        <v>188.964</v>
       </c>
       <c r="G37">
         <v>72.09999999999999</v>
@@ -4315,45 +4315,45 @@
         <v>36.2</v>
       </c>
       <c r="M37">
-        <v>11.7761315</v>
+        <v>13.5865116</v>
       </c>
       <c r="N37">
-        <v>24.4238685</v>
+        <v>22.6134884</v>
       </c>
       <c r="O37">
-        <v>5.495370412500001</v>
+        <v>5.08803489</v>
       </c>
       <c r="P37">
-        <v>18.9284980875</v>
+        <v>17.52545351</v>
       </c>
       <c r="Q37">
-        <v>32.3284980875</v>
+        <v>30.92545351</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.2186646754194062</v>
+        <v>0.2209368959663879</v>
       </c>
       <c r="T37">
-        <v>1.205289019123933</v>
+        <v>1.221131946359703</v>
       </c>
       <c r="U37">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V37">
         <v>0.225</v>
       </c>
       <c r="W37">
-        <v>0.04967750000000001</v>
+        <v>0.05572250000000001</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y37">
-        <v>3.074014586199211</v>
+        <v>2.664407249319244</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1614597134184882</v>
+        <v>0.1612845128143625</v>
       </c>
       <c r="C38">
-        <v>410.9268978096034</v>
+        <v>406.4786050377403</v>
       </c>
       <c r="D38">
-        <v>527.7908978096034</v>
+        <v>528.5916050377402</v>
       </c>
       <c r="E38">
-        <v>-59.23599999999999</v>
+        <v>-53.98699999999999</v>
       </c>
       <c r="F38">
-        <v>188.964</v>
+        <v>194.213</v>
       </c>
       <c r="G38">
         <v>72.09999999999999</v>
@@ -4397,28 +4397,28 @@
         <v>36.2</v>
       </c>
       <c r="M38">
-        <v>13.5865116</v>
+        <v>13.9639147</v>
       </c>
       <c r="N38">
-        <v>22.6134884</v>
+        <v>22.2360853</v>
       </c>
       <c r="O38">
-        <v>5.08803489</v>
+        <v>5.003119192500001</v>
       </c>
       <c r="P38">
-        <v>17.52545351</v>
+        <v>17.2329661075</v>
       </c>
       <c r="Q38">
-        <v>30.92545351</v>
+        <v>30.6329661075</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.2209368959663879</v>
+        <v>0.223281250498988</v>
       </c>
       <c r="T38">
-        <v>1.221131946359703</v>
+        <v>1.237477823666451</v>
       </c>
       <c r="U38">
         <v>0.07190000000000001</v>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>2.664407249319244</v>
+        <v>2.592396242580886</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1612845128143625</v>
+        <v>0.1611093122102367</v>
       </c>
       <c r="C39">
-        <v>406.4786050377403</v>
+        <v>402.0327454499351</v>
       </c>
       <c r="D39">
-        <v>528.5916050377402</v>
+        <v>529.394745449935</v>
       </c>
       <c r="E39">
-        <v>-53.98699999999999</v>
+        <v>-48.738</v>
       </c>
       <c r="F39">
-        <v>194.213</v>
+        <v>199.462</v>
       </c>
       <c r="G39">
         <v>72.09999999999999</v>
@@ -4479,28 +4479,28 @@
         <v>36.2</v>
       </c>
       <c r="M39">
-        <v>13.9639147</v>
+        <v>14.3413178</v>
       </c>
       <c r="N39">
-        <v>22.2360853</v>
+        <v>21.8586822</v>
       </c>
       <c r="O39">
-        <v>5.003119192500001</v>
+        <v>4.918203495000001</v>
       </c>
       <c r="P39">
-        <v>17.2329661075</v>
+        <v>16.940478705</v>
       </c>
       <c r="Q39">
-        <v>30.6329661075</v>
+        <v>30.340478705</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.223281250498988</v>
+        <v>0.2257012293713495</v>
       </c>
       <c r="T39">
-        <v>1.237477823666451</v>
+        <v>1.254350987337933</v>
       </c>
       <c r="U39">
         <v>0.07190000000000001</v>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>2.592396242580886</v>
+        <v>2.524175288828758</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1611093122102367</v>
+        <v>0.1621128866061109</v>
       </c>
       <c r="C40">
-        <v>402.0327454499351</v>
+        <v>392.2160055601746</v>
       </c>
       <c r="D40">
-        <v>529.394745449935</v>
+        <v>524.8270055601746</v>
       </c>
       <c r="E40">
-        <v>-48.738</v>
+        <v>-43.489</v>
       </c>
       <c r="F40">
-        <v>199.462</v>
+        <v>204.711</v>
       </c>
       <c r="G40">
         <v>72.09999999999999</v>
@@ -4561,45 +4561,45 @@
         <v>36.2</v>
       </c>
       <c r="M40">
-        <v>14.3413178</v>
+        <v>15.5170938</v>
       </c>
       <c r="N40">
-        <v>21.8586822</v>
+        <v>20.68290620000001</v>
       </c>
       <c r="O40">
-        <v>4.918203495000001</v>
+        <v>4.653653895000001</v>
       </c>
       <c r="P40">
-        <v>16.940478705</v>
+        <v>16.029252305</v>
       </c>
       <c r="Q40">
-        <v>30.340478705</v>
+        <v>29.42925230500001</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.2257012293713495</v>
+        <v>0.2282005518132965</v>
       </c>
       <c r="T40">
-        <v>1.254350987337933</v>
+        <v>1.271777369490446</v>
       </c>
       <c r="U40">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V40">
         <v>0.225</v>
       </c>
       <c r="W40">
-        <v>0.05572250000000001</v>
+        <v>0.05874500000000001</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y40">
-        <v>2.524175288828758</v>
+        <v>2.3329110764285</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1621128866061109</v>
+        <v>0.1619679110019851</v>
       </c>
       <c r="C41">
-        <v>392.2160055601746</v>
+        <v>387.6219808587432</v>
       </c>
       <c r="D41">
-        <v>524.8270055601746</v>
+        <v>525.4819808587432</v>
       </c>
       <c r="E41">
-        <v>-43.489</v>
+        <v>-38.23999999999998</v>
       </c>
       <c r="F41">
-        <v>204.711</v>
+        <v>209.96</v>
       </c>
       <c r="G41">
         <v>72.09999999999999</v>
@@ -4643,28 +4643,28 @@
         <v>36.2</v>
       </c>
       <c r="M41">
-        <v>15.5170938</v>
+        <v>15.914968</v>
       </c>
       <c r="N41">
-        <v>20.68290620000001</v>
+        <v>20.285032</v>
       </c>
       <c r="O41">
-        <v>4.653653895000001</v>
+        <v>4.5641322</v>
       </c>
       <c r="P41">
-        <v>16.029252305</v>
+        <v>15.7208998</v>
       </c>
       <c r="Q41">
-        <v>29.42925230500001</v>
+        <v>29.1208998</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.2282005518132965</v>
+        <v>0.2307831850033085</v>
       </c>
       <c r="T41">
-        <v>1.271777369490446</v>
+        <v>1.289784631048044</v>
       </c>
       <c r="U41">
         <v>0.07580000000000001</v>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.3329110764285</v>
+        <v>2.274588299517787</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1619679110019851</v>
+        <v>0.1618229353978593</v>
       </c>
       <c r="C42">
-        <v>387.6219808587432</v>
+        <v>383.0295929964295</v>
       </c>
       <c r="D42">
-        <v>525.4819808587432</v>
+        <v>526.1385929964295</v>
       </c>
       <c r="E42">
-        <v>-38.23999999999998</v>
+        <v>-32.99099999999999</v>
       </c>
       <c r="F42">
-        <v>209.96</v>
+        <v>215.209</v>
       </c>
       <c r="G42">
         <v>72.09999999999999</v>
@@ -4725,28 +4725,28 @@
         <v>36.2</v>
       </c>
       <c r="M42">
-        <v>15.914968</v>
+        <v>16.3128422</v>
       </c>
       <c r="N42">
-        <v>20.285032</v>
+        <v>19.8871578</v>
       </c>
       <c r="O42">
-        <v>4.5641322</v>
+        <v>4.474610505</v>
       </c>
       <c r="P42">
-        <v>15.7208998</v>
+        <v>15.412547295</v>
       </c>
       <c r="Q42">
-        <v>29.1208998</v>
+        <v>28.812547295</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.2307831850033085</v>
+        <v>0.2334533650811175</v>
       </c>
       <c r="T42">
-        <v>1.289784631048044</v>
+        <v>1.308402308251662</v>
       </c>
       <c r="U42">
         <v>0.07580000000000001</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.274588299517787</v>
+        <v>2.219110536114914</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1618229353978593</v>
+        <v>0.1616779597937335</v>
       </c>
       <c r="C43">
-        <v>383.0295929964295</v>
+        <v>378.4388481168107</v>
       </c>
       <c r="D43">
-        <v>526.1385929964295</v>
+        <v>526.7968481168107</v>
       </c>
       <c r="E43">
-        <v>-32.99099999999999</v>
+        <v>-27.74199999999999</v>
       </c>
       <c r="F43">
-        <v>215.209</v>
+        <v>220.458</v>
       </c>
       <c r="G43">
         <v>72.09999999999999</v>
@@ -4807,28 +4807,28 @@
         <v>36.2</v>
       </c>
       <c r="M43">
-        <v>16.3128422</v>
+        <v>16.7107164</v>
       </c>
       <c r="N43">
-        <v>19.8871578</v>
+        <v>19.4892836</v>
       </c>
       <c r="O43">
-        <v>4.474610505</v>
+        <v>4.38508881</v>
       </c>
       <c r="P43">
-        <v>15.412547295</v>
+        <v>15.10419479</v>
       </c>
       <c r="Q43">
-        <v>28.812547295</v>
+        <v>28.50419479</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.2334533650811175</v>
+        <v>0.2362156203340233</v>
       </c>
       <c r="T43">
-        <v>1.308402308251662</v>
+        <v>1.327661974324369</v>
       </c>
       <c r="U43">
         <v>0.07580000000000001</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.219110536114914</v>
+        <v>2.166274570969321</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1616779597937335</v>
+        <v>0.1615329841896078</v>
       </c>
       <c r="C44">
-        <v>378.4388481168106</v>
+        <v>373.8497523942476</v>
       </c>
       <c r="D44">
-        <v>526.7968481168106</v>
+        <v>527.4567523942476</v>
       </c>
       <c r="E44">
-        <v>-27.74200000000002</v>
+        <v>-22.49299999999999</v>
       </c>
       <c r="F44">
-        <v>220.458</v>
+        <v>225.707</v>
       </c>
       <c r="G44">
         <v>72.09999999999999</v>
@@ -4889,28 +4889,28 @@
         <v>36.2</v>
       </c>
       <c r="M44">
-        <v>16.7107164</v>
+        <v>17.1085906</v>
       </c>
       <c r="N44">
-        <v>19.4892836</v>
+        <v>19.0914094</v>
       </c>
       <c r="O44">
-        <v>4.385088810000001</v>
+        <v>4.295567115000001</v>
       </c>
       <c r="P44">
-        <v>15.10419479</v>
+        <v>14.795842285</v>
       </c>
       <c r="Q44">
-        <v>28.50419479</v>
+        <v>28.195842285</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.2362156203340233</v>
+        <v>0.2390747968238732</v>
       </c>
       <c r="T44">
-        <v>1.327661974324369</v>
+        <v>1.347597418154014</v>
       </c>
       <c r="U44">
         <v>0.07580000000000001</v>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.166274570969321</v>
+        <v>2.115896092574686</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1615329841896078</v>
+        <v>0.1613880085854819</v>
       </c>
       <c r="C45">
-        <v>373.8497523942476</v>
+        <v>369.2623120340787</v>
       </c>
       <c r="D45">
-        <v>527.4567523942476</v>
+        <v>528.1183120340787</v>
       </c>
       <c r="E45">
-        <v>-22.49299999999999</v>
+        <v>-17.244</v>
       </c>
       <c r="F45">
-        <v>225.707</v>
+        <v>230.956</v>
       </c>
       <c r="G45">
         <v>72.09999999999999</v>
@@ -4971,28 +4971,28 @@
         <v>36.2</v>
       </c>
       <c r="M45">
-        <v>17.1085906</v>
+        <v>17.5064648</v>
       </c>
       <c r="N45">
-        <v>19.0914094</v>
+        <v>18.6935352</v>
       </c>
       <c r="O45">
-        <v>4.295567115000001</v>
+        <v>4.206045420000001</v>
       </c>
       <c r="P45">
-        <v>14.795842285</v>
+        <v>14.48748978</v>
       </c>
       <c r="Q45">
-        <v>28.195842285</v>
+        <v>27.88748978</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.2390747968238732</v>
+        <v>0.2420360867597892</v>
       </c>
       <c r="T45">
-        <v>1.347597418154014</v>
+        <v>1.368244842120433</v>
       </c>
       <c r="U45">
         <v>0.07580000000000001</v>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.115896092574686</v>
+        <v>2.06780754501617</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1613880085854819</v>
+        <v>0.1612430329813561</v>
       </c>
       <c r="C46">
-        <v>369.2623120340787</v>
+        <v>364.6765332728122</v>
       </c>
       <c r="D46">
-        <v>528.1183120340787</v>
+        <v>528.7815332728121</v>
       </c>
       <c r="E46">
-        <v>-17.244</v>
+        <v>-11.995</v>
       </c>
       <c r="F46">
-        <v>230.956</v>
+        <v>236.205</v>
       </c>
       <c r="G46">
         <v>72.09999999999999</v>
@@ -5053,28 +5053,28 @@
         <v>36.2</v>
       </c>
       <c r="M46">
-        <v>17.5064648</v>
+        <v>17.904339</v>
       </c>
       <c r="N46">
-        <v>18.6935352</v>
+        <v>18.295661</v>
       </c>
       <c r="O46">
-        <v>4.206045420000001</v>
+        <v>4.116523725</v>
       </c>
       <c r="P46">
-        <v>14.48748978</v>
+        <v>14.179137275</v>
       </c>
       <c r="Q46">
-        <v>27.88748978</v>
+        <v>27.579137275</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.2420360867597892</v>
+        <v>0.2451050599661021</v>
       </c>
       <c r="T46">
-        <v>1.368244842120433</v>
+        <v>1.389643081503811</v>
       </c>
       <c r="U46">
         <v>0.07580000000000001</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.06780754501617</v>
+        <v>2.021856266238033</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1612430329813561</v>
+        <v>0.1661603573772304</v>
       </c>
       <c r="C47">
-        <v>364.6765332728122</v>
+        <v>337.8241549652792</v>
       </c>
       <c r="D47">
-        <v>528.7815332728121</v>
+        <v>507.1781549652792</v>
       </c>
       <c r="E47">
-        <v>-11.995</v>
+        <v>-6.745999999999981</v>
       </c>
       <c r="F47">
-        <v>236.205</v>
+        <v>241.454</v>
       </c>
       <c r="G47">
         <v>72.09999999999999</v>
@@ -5135,45 +5135,45 @@
         <v>36.2</v>
       </c>
       <c r="M47">
-        <v>17.904339</v>
+        <v>21.73086</v>
       </c>
       <c r="N47">
-        <v>18.295661</v>
+        <v>14.46914</v>
       </c>
       <c r="O47">
-        <v>4.116523725</v>
+        <v>3.255556500000001</v>
       </c>
       <c r="P47">
-        <v>14.179137275</v>
+        <v>11.2135835</v>
       </c>
       <c r="Q47">
-        <v>27.579137275</v>
+        <v>24.6135835</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.2451050599661021</v>
+        <v>0.2482876988467229</v>
       </c>
       <c r="T47">
-        <v>1.389643081503811</v>
+        <v>1.41183384827176</v>
       </c>
       <c r="U47">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V47">
         <v>0.225</v>
       </c>
       <c r="W47">
-        <v>0.05874500000000001</v>
+        <v>0.06974999999999999</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y47">
-        <v>2.021856266238033</v>
+        <v>1.665833749791771</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1661603573772304</v>
+        <v>0.1661254317731046</v>
       </c>
       <c r="C48">
-        <v>337.8241549652792</v>
+        <v>332.7223682617581</v>
       </c>
       <c r="D48">
-        <v>507.1781549652792</v>
+        <v>507.3253682617581</v>
       </c>
       <c r="E48">
-        <v>-6.745999999999981</v>
+        <v>-1.496999999999986</v>
       </c>
       <c r="F48">
-        <v>241.454</v>
+        <v>246.703</v>
       </c>
       <c r="G48">
         <v>72.09999999999999</v>
@@ -5217,28 +5217,28 @@
         <v>36.2</v>
       </c>
       <c r="M48">
-        <v>21.73086</v>
+        <v>22.20327</v>
       </c>
       <c r="N48">
-        <v>14.46914</v>
+        <v>13.99673</v>
       </c>
       <c r="O48">
-        <v>3.255556500000001</v>
+        <v>3.149264250000001</v>
       </c>
       <c r="P48">
-        <v>11.2135835</v>
+        <v>10.84746575</v>
       </c>
       <c r="Q48">
-        <v>24.6135835</v>
+        <v>24.24746575</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.2482876988467229</v>
+        <v>0.2515904373077445</v>
       </c>
       <c r="T48">
-        <v>1.41183384827176</v>
+        <v>1.434862002464914</v>
       </c>
       <c r="U48">
         <v>0.09</v>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>1.665833749791771</v>
+        <v>1.630390478519606</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1661254317731046</v>
+        <v>0.1660905061689788</v>
       </c>
       <c r="C49">
-        <v>332.7223682617581</v>
+        <v>327.6206670431762</v>
       </c>
       <c r="D49">
-        <v>507.3253682617581</v>
+        <v>507.4726670431763</v>
       </c>
       <c r="E49">
-        <v>-1.496999999999986</v>
+        <v>3.75200000000001</v>
       </c>
       <c r="F49">
-        <v>246.703</v>
+        <v>251.952</v>
       </c>
       <c r="G49">
         <v>72.09999999999999</v>
@@ -5299,28 +5299,28 @@
         <v>36.2</v>
       </c>
       <c r="M49">
-        <v>22.20327</v>
+        <v>22.67568</v>
       </c>
       <c r="N49">
-        <v>13.99673</v>
+        <v>13.52432</v>
       </c>
       <c r="O49">
-        <v>3.149264250000001</v>
+        <v>3.042972000000001</v>
       </c>
       <c r="P49">
-        <v>10.84746575</v>
+        <v>10.481348</v>
       </c>
       <c r="Q49">
-        <v>24.24746575</v>
+        <v>23.881348</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.2515904373077445</v>
+        <v>0.255020204171113</v>
       </c>
       <c r="T49">
-        <v>1.434862002464914</v>
+        <v>1.458775854896266</v>
       </c>
       <c r="U49">
         <v>0.09</v>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>1.630390478519606</v>
+        <v>1.596424010217114</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1660905061689788</v>
+        <v>0.166055580564853</v>
       </c>
       <c r="C50">
-        <v>327.6206670431762</v>
+        <v>322.5190513840158</v>
       </c>
       <c r="D50">
-        <v>507.4726670431763</v>
+        <v>507.6200513840157</v>
       </c>
       <c r="E50">
-        <v>3.751999999999981</v>
+        <v>9.000999999999976</v>
       </c>
       <c r="F50">
-        <v>251.952</v>
+        <v>257.201</v>
       </c>
       <c r="G50">
         <v>72.09999999999999</v>
@@ -5381,28 +5381,28 @@
         <v>36.2</v>
       </c>
       <c r="M50">
-        <v>22.67568</v>
+        <v>23.14809</v>
       </c>
       <c r="N50">
-        <v>13.52432000000001</v>
+        <v>13.05191000000001</v>
       </c>
       <c r="O50">
-        <v>3.042972000000002</v>
+        <v>2.936679750000001</v>
       </c>
       <c r="P50">
-        <v>10.481348</v>
+        <v>10.11523025000001</v>
       </c>
       <c r="Q50">
-        <v>23.881348</v>
+        <v>23.51523025000001</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.255020204171113</v>
+        <v>0.2585844716957902</v>
       </c>
       <c r="T50">
-        <v>1.458775854896266</v>
+        <v>1.483627505462181</v>
       </c>
       <c r="U50">
         <v>0.09</v>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>1.596424010217114</v>
+        <v>1.563843928375948</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.166055580564853</v>
+        <v>0.1660206549607272</v>
       </c>
       <c r="C51">
-        <v>322.5190513840158</v>
+        <v>317.4175213588446</v>
       </c>
       <c r="D51">
-        <v>507.6200513840157</v>
+        <v>507.7675213588445</v>
       </c>
       <c r="E51">
-        <v>9.000999999999976</v>
+        <v>14.25</v>
       </c>
       <c r="F51">
-        <v>257.201</v>
+        <v>262.45</v>
       </c>
       <c r="G51">
         <v>72.09999999999999</v>
@@ -5463,28 +5463,28 @@
         <v>36.2</v>
       </c>
       <c r="M51">
-        <v>23.14809</v>
+        <v>23.6205</v>
       </c>
       <c r="N51">
-        <v>13.05191000000001</v>
+        <v>12.5795</v>
       </c>
       <c r="O51">
-        <v>2.936679750000001</v>
+        <v>2.830387500000001</v>
       </c>
       <c r="P51">
-        <v>10.11523025000001</v>
+        <v>9.749112500000003</v>
       </c>
       <c r="Q51">
-        <v>23.51523025000001</v>
+        <v>23.1491125</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.2585844716957902</v>
+        <v>0.2622913099214544</v>
       </c>
       <c r="T51">
-        <v>1.483627505462181</v>
+        <v>1.509473222050732</v>
       </c>
       <c r="U51">
         <v>0.09</v>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>1.563843928375948</v>
+        <v>1.532567049808429</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1660206549607272</v>
+        <v>0.1659857293566014</v>
       </c>
       <c r="C52">
-        <v>317.4175213588446</v>
+        <v>312.3160770423173</v>
       </c>
       <c r="D52">
-        <v>507.7675213588445</v>
+        <v>507.9150770423174</v>
       </c>
       <c r="E52">
-        <v>14.25</v>
+        <v>19.49900000000002</v>
       </c>
       <c r="F52">
-        <v>262.45</v>
+        <v>267.699</v>
       </c>
       <c r="G52">
         <v>72.09999999999999</v>
@@ -5545,28 +5545,28 @@
         <v>36.2</v>
       </c>
       <c r="M52">
-        <v>23.6205</v>
+        <v>24.09291</v>
       </c>
       <c r="N52">
-        <v>12.5795</v>
+        <v>12.10709</v>
       </c>
       <c r="O52">
-        <v>2.830387500000001</v>
+        <v>2.724095250000001</v>
       </c>
       <c r="P52">
-        <v>9.749112500000003</v>
+        <v>9.382994750000002</v>
       </c>
       <c r="Q52">
-        <v>23.1491125</v>
+        <v>22.78299475</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.2622913099214544</v>
+        <v>0.2661494476665335</v>
       </c>
       <c r="T52">
-        <v>1.509473222050732</v>
+        <v>1.53637386584698</v>
       </c>
       <c r="U52">
         <v>0.09</v>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>1.532567049808429</v>
+        <v>1.50251671549846</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1659857293566014</v>
+        <v>0.1918773887926021</v>
       </c>
       <c r="C53">
-        <v>312.3160770423173</v>
+        <v>217.0410688703003</v>
       </c>
       <c r="D53">
-        <v>507.9150770423174</v>
+        <v>417.8890688703003</v>
       </c>
       <c r="E53">
-        <v>19.49900000000002</v>
+        <v>24.74799999999999</v>
       </c>
       <c r="F53">
-        <v>267.699</v>
+        <v>272.948</v>
       </c>
       <c r="G53">
         <v>72.09999999999999</v>
@@ -5627,45 +5627,45 @@
         <v>36.2</v>
       </c>
       <c r="M53">
-        <v>24.09291</v>
+        <v>40.0687664</v>
       </c>
       <c r="N53">
-        <v>12.10709</v>
+        <v>-3.868766399999998</v>
       </c>
       <c r="O53">
-        <v>2.724095250000001</v>
+        <v>-0.8704724399999997</v>
       </c>
       <c r="P53">
-        <v>9.382994750000002</v>
+        <v>-2.998293959999999</v>
       </c>
       <c r="Q53">
-        <v>22.78299475</v>
+        <v>10.40170604</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.2661494476665335</v>
+        <v>0.2730388128581508</v>
       </c>
       <c r="T53">
-        <v>1.53637386584698</v>
+        <v>1.584409568884888</v>
       </c>
       <c r="U53">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V53">
-        <v>0.225</v>
+        <v>0.2032755368281066</v>
       </c>
       <c r="W53">
-        <v>0.06974999999999999</v>
+        <v>0.116959151193634</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y53">
-        <v>1.50251671549846</v>
+        <v>0.9034468303471405</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1918773887926021</v>
+        <v>0.1928873887926021</v>
       </c>
       <c r="C54">
-        <v>217.0410688703003</v>
+        <v>208.9225641287746</v>
       </c>
       <c r="D54">
-        <v>417.8890688703003</v>
+        <v>415.0195641287747</v>
       </c>
       <c r="E54">
-        <v>24.74799999999999</v>
+        <v>29.99700000000001</v>
       </c>
       <c r="F54">
-        <v>272.948</v>
+        <v>278.197</v>
       </c>
       <c r="G54">
         <v>72.09999999999999</v>
@@ -5709,37 +5709,37 @@
         <v>36.2</v>
       </c>
       <c r="M54">
-        <v>40.0687664</v>
+        <v>40.8393196</v>
       </c>
       <c r="N54">
-        <v>-3.868766399999998</v>
+        <v>-4.6393196</v>
       </c>
       <c r="O54">
-        <v>-0.8704724399999997</v>
+        <v>-1.04384691</v>
       </c>
       <c r="P54">
-        <v>-2.998293959999999</v>
+        <v>-3.59547269</v>
       </c>
       <c r="Q54">
-        <v>10.40170604</v>
+        <v>9.804527310000001</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.2730388128581508</v>
+        <v>0.2778736812168349</v>
       </c>
       <c r="T54">
-        <v>1.584409568884888</v>
+        <v>1.618120410776057</v>
       </c>
       <c r="U54">
         <v>0.1468</v>
       </c>
       <c r="V54">
-        <v>0.2032755368281066</v>
+        <v>0.1994401493407838</v>
       </c>
       <c r="W54">
-        <v>0.116959151193634</v>
+        <v>0.1175221860767729</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.9034468303471405</v>
+        <v>0.886400663736817</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1928873887926021</v>
+        <v>0.193897388792602</v>
       </c>
       <c r="C55">
-        <v>208.9225641287746</v>
+        <v>200.8431984944617</v>
       </c>
       <c r="D55">
-        <v>415.0195641287747</v>
+        <v>412.1891984944618</v>
       </c>
       <c r="E55">
-        <v>29.99700000000001</v>
+        <v>35.24600000000004</v>
       </c>
       <c r="F55">
-        <v>278.197</v>
+        <v>283.446</v>
       </c>
       <c r="G55">
         <v>72.09999999999999</v>
@@ -5791,37 +5791,37 @@
         <v>36.2</v>
       </c>
       <c r="M55">
-        <v>40.8393196</v>
+        <v>41.60987280000001</v>
       </c>
       <c r="N55">
-        <v>-4.6393196</v>
+        <v>-5.409872800000002</v>
       </c>
       <c r="O55">
-        <v>-1.04384691</v>
+        <v>-1.21722138</v>
       </c>
       <c r="P55">
-        <v>-3.59547269</v>
+        <v>-4.192651420000002</v>
       </c>
       <c r="Q55">
-        <v>9.804527310000001</v>
+        <v>9.207348579999998</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.2778736812168349</v>
+        <v>0.2829187612432878</v>
       </c>
       <c r="T55">
-        <v>1.618120410776057</v>
+        <v>1.653296941445101</v>
       </c>
       <c r="U55">
         <v>0.1468</v>
       </c>
       <c r="V55">
-        <v>0.1994401493407838</v>
+        <v>0.1957468132418804</v>
       </c>
       <c r="W55">
-        <v>0.1175221860767729</v>
+        <v>0.118064367816092</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.886400663736817</v>
+        <v>0.8699858366305796</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.193897388792602</v>
+        <v>0.194907388792602</v>
       </c>
       <c r="C56">
-        <v>200.8431984944617</v>
+        <v>192.8021766245163</v>
       </c>
       <c r="D56">
-        <v>412.1891984944618</v>
+        <v>409.3971766245164</v>
       </c>
       <c r="E56">
-        <v>35.24600000000004</v>
+        <v>40.495</v>
       </c>
       <c r="F56">
-        <v>283.446</v>
+        <v>288.695</v>
       </c>
       <c r="G56">
         <v>72.09999999999999</v>
@@ -5873,37 +5873,37 @@
         <v>36.2</v>
       </c>
       <c r="M56">
-        <v>41.60987280000001</v>
+        <v>42.380426</v>
       </c>
       <c r="N56">
-        <v>-5.409872800000002</v>
+        <v>-6.180425999999997</v>
       </c>
       <c r="O56">
-        <v>-1.21722138</v>
+        <v>-1.390595849999999</v>
       </c>
       <c r="P56">
-        <v>-4.192651420000002</v>
+        <v>-4.789830149999998</v>
       </c>
       <c r="Q56">
-        <v>9.207348579999998</v>
+        <v>8.610169850000002</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.2829187612432878</v>
+        <v>0.2881880670486942</v>
       </c>
       <c r="T56">
-        <v>1.653296941445101</v>
+        <v>1.690036873477214</v>
       </c>
       <c r="U56">
         <v>0.1468</v>
       </c>
       <c r="V56">
-        <v>0.1957468132418804</v>
+        <v>0.1921877802738463</v>
       </c>
       <c r="W56">
-        <v>0.118064367816092</v>
+        <v>0.1185868338557994</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.8699858366305796</v>
+        <v>0.8541679123282055</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.194907388792602</v>
+        <v>0.1959173887926021</v>
       </c>
       <c r="C57">
-        <v>192.8021766245163</v>
+        <v>184.7987245805759</v>
       </c>
       <c r="D57">
-        <v>409.3971766245164</v>
+        <v>406.6427245805759</v>
       </c>
       <c r="E57">
-        <v>40.495</v>
+        <v>45.74400000000003</v>
       </c>
       <c r="F57">
-        <v>288.695</v>
+        <v>293.944</v>
       </c>
       <c r="G57">
         <v>72.09999999999999</v>
@@ -5955,37 +5955,37 @@
         <v>36.2</v>
       </c>
       <c r="M57">
-        <v>42.380426</v>
+        <v>43.15097920000001</v>
       </c>
       <c r="N57">
-        <v>-6.180425999999997</v>
+        <v>-6.950979200000006</v>
       </c>
       <c r="O57">
-        <v>-1.390595849999999</v>
+        <v>-1.563970320000001</v>
       </c>
       <c r="P57">
-        <v>-4.789830149999998</v>
+        <v>-5.387008880000005</v>
       </c>
       <c r="Q57">
-        <v>8.610169850000002</v>
+        <v>8.012991119999995</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2881880670486942</v>
+        <v>0.2936968867543464</v>
       </c>
       <c r="T57">
-        <v>1.690036873477214</v>
+        <v>1.728446802419879</v>
       </c>
       <c r="U57">
         <v>0.1468</v>
       </c>
       <c r="V57">
-        <v>0.1921877802738463</v>
+        <v>0.188755855626099</v>
       </c>
       <c r="W57">
-        <v>0.1185868338557994</v>
+        <v>0.1190906403940887</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.8541679123282055</v>
+        <v>0.8389149138937732</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1959173887926021</v>
+        <v>0.1969273887926021</v>
       </c>
       <c r="C58">
-        <v>184.7987245805759</v>
+        <v>176.8320891135197</v>
       </c>
       <c r="D58">
-        <v>406.6427245805759</v>
+        <v>403.9250891135197</v>
       </c>
       <c r="E58">
-        <v>45.74400000000003</v>
+        <v>50.99300000000005</v>
       </c>
       <c r="F58">
-        <v>293.944</v>
+        <v>299.193</v>
       </c>
       <c r="G58">
         <v>72.09999999999999</v>
@@ -6037,37 +6037,37 @@
         <v>36.2</v>
       </c>
       <c r="M58">
-        <v>43.15097920000001</v>
+        <v>43.92153240000001</v>
       </c>
       <c r="N58">
-        <v>-6.950979200000006</v>
+        <v>-7.721532400000008</v>
       </c>
       <c r="O58">
-        <v>-1.563970320000001</v>
+        <v>-1.737344790000002</v>
       </c>
       <c r="P58">
-        <v>-5.387008880000005</v>
+        <v>-5.984187610000006</v>
       </c>
       <c r="Q58">
-        <v>8.012991119999995</v>
+        <v>7.415812389999994</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2936968867543464</v>
+        <v>0.2994619306323545</v>
       </c>
       <c r="T58">
-        <v>1.728446802419879</v>
+        <v>1.768643239685457</v>
       </c>
       <c r="U58">
         <v>0.1468</v>
       </c>
       <c r="V58">
-        <v>0.188755855626099</v>
+        <v>0.1854443493870446</v>
       </c>
       <c r="W58">
-        <v>0.1190906403940887</v>
+        <v>0.1195767695099819</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.8389149138937732</v>
+        <v>0.8241971083868648</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1969273887926021</v>
+        <v>0.1979373887926021</v>
       </c>
       <c r="C59">
-        <v>176.8320891135197</v>
+        <v>168.9015369767152</v>
       </c>
       <c r="D59">
-        <v>403.9250891135197</v>
+        <v>401.2435369767152</v>
       </c>
       <c r="E59">
-        <v>50.99300000000005</v>
+        <v>56.24200000000002</v>
       </c>
       <c r="F59">
-        <v>299.193</v>
+        <v>304.442</v>
       </c>
       <c r="G59">
         <v>72.09999999999999</v>
@@ -6119,37 +6119,37 @@
         <v>36.2</v>
       </c>
       <c r="M59">
-        <v>43.92153240000001</v>
+        <v>44.69208560000001</v>
       </c>
       <c r="N59">
-        <v>-7.721532400000008</v>
+        <v>-8.492085600000003</v>
       </c>
       <c r="O59">
-        <v>-1.737344790000002</v>
+        <v>-1.910719260000001</v>
       </c>
       <c r="P59">
-        <v>-5.984187610000006</v>
+        <v>-6.581366340000002</v>
       </c>
       <c r="Q59">
-        <v>7.415812389999994</v>
+        <v>6.818633659999998</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2994619306323545</v>
+        <v>0.3055015004093153</v>
       </c>
       <c r="T59">
-        <v>1.768643239685457</v>
+        <v>1.810753793011302</v>
       </c>
       <c r="U59">
         <v>0.1468</v>
       </c>
       <c r="V59">
-        <v>0.1854443493870446</v>
+        <v>0.1822470330183025</v>
       </c>
       <c r="W59">
-        <v>0.1195767695099819</v>
+        <v>0.1200461355529132</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.8241971083868648</v>
+        <v>0.8099868134146776</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1979373887926021</v>
+        <v>0.2342744429247516</v>
       </c>
       <c r="C60">
-        <v>168.9015369767152</v>
+        <v>86.29452547634907</v>
       </c>
       <c r="D60">
-        <v>401.2435369767152</v>
+        <v>323.8855254763491</v>
       </c>
       <c r="E60">
-        <v>56.24199999999996</v>
+        <v>61.49099999999999</v>
       </c>
       <c r="F60">
-        <v>304.442</v>
+        <v>309.691</v>
       </c>
       <c r="G60">
         <v>72.09999999999999</v>
@@ -6201,45 +6201,45 @@
         <v>36.2</v>
       </c>
       <c r="M60">
-        <v>44.6920856</v>
+        <v>62.1859528</v>
       </c>
       <c r="N60">
-        <v>-8.492085599999996</v>
+        <v>-25.98595279999999</v>
       </c>
       <c r="O60">
-        <v>-1.910719259999999</v>
+        <v>-5.846839379999999</v>
       </c>
       <c r="P60">
-        <v>-6.581366339999997</v>
+        <v>-20.13911341999999</v>
       </c>
       <c r="Q60">
-        <v>6.818633660000003</v>
+        <v>-6.739113419999994</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.3055015004093152</v>
+        <v>0.3202919129367364</v>
       </c>
       <c r="T60">
-        <v>1.810753793011301</v>
+        <v>1.913879094721222</v>
       </c>
       <c r="U60">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V60">
-        <v>0.1822470330183025</v>
+        <v>0.1309781330551552</v>
       </c>
       <c r="W60">
-        <v>0.1200461355529132</v>
+        <v>0.1744995908825248</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y60">
-        <v>0.8099868134146777</v>
+        <v>0.5821250358006897</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2342744429247516</v>
+        <v>0.2358244429247516</v>
       </c>
       <c r="C61">
-        <v>86.29452547634907</v>
+        <v>78.40364132312385</v>
       </c>
       <c r="D61">
-        <v>323.8855254763491</v>
+        <v>321.2436413231239</v>
       </c>
       <c r="E61">
-        <v>61.49099999999999</v>
+        <v>66.74000000000001</v>
       </c>
       <c r="F61">
-        <v>309.691</v>
+        <v>314.94</v>
       </c>
       <c r="G61">
         <v>72.09999999999999</v>
@@ -6283,37 +6283,37 @@
         <v>36.2</v>
       </c>
       <c r="M61">
-        <v>62.1859528</v>
+        <v>63.239952</v>
       </c>
       <c r="N61">
-        <v>-25.98595279999999</v>
+        <v>-27.039952</v>
       </c>
       <c r="O61">
-        <v>-5.846839379999999</v>
+        <v>-6.0839892</v>
       </c>
       <c r="P61">
-        <v>-20.13911341999999</v>
+        <v>-20.9559628</v>
       </c>
       <c r="Q61">
-        <v>-6.739113419999994</v>
+        <v>-7.555962799999998</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.3202919129367364</v>
+        <v>0.3271542107601548</v>
       </c>
       <c r="T61">
-        <v>1.913879094721222</v>
+        <v>1.961726072089252</v>
       </c>
       <c r="U61">
         <v>0.2008</v>
       </c>
       <c r="V61">
-        <v>0.1309781330551552</v>
+        <v>0.1287951641709026</v>
       </c>
       <c r="W61">
-        <v>0.1744995908825248</v>
+        <v>0.1749379310344827</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.5821250358006897</v>
+        <v>0.5724229518706783</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2358244429247516</v>
+        <v>0.2373744429247516</v>
       </c>
       <c r="C62">
-        <v>78.40364132312385</v>
+        <v>70.55550734445205</v>
       </c>
       <c r="D62">
-        <v>321.2436413231239</v>
+        <v>318.644507344452</v>
       </c>
       <c r="E62">
-        <v>66.74000000000001</v>
+        <v>71.98899999999998</v>
       </c>
       <c r="F62">
-        <v>314.94</v>
+        <v>320.189</v>
       </c>
       <c r="G62">
         <v>72.09999999999999</v>
@@ -6365,37 +6365,37 @@
         <v>36.2</v>
       </c>
       <c r="M62">
-        <v>63.239952</v>
+        <v>64.2939512</v>
       </c>
       <c r="N62">
-        <v>-27.039952</v>
+        <v>-28.09395119999999</v>
       </c>
       <c r="O62">
-        <v>-6.0839892</v>
+        <v>-6.321139019999999</v>
       </c>
       <c r="P62">
-        <v>-20.9559628</v>
+        <v>-21.77281218</v>
       </c>
       <c r="Q62">
-        <v>-7.555962799999998</v>
+        <v>-8.372812179999995</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.3271542107601548</v>
+        <v>0.3343684212924665</v>
       </c>
       <c r="T62">
-        <v>1.961726072089252</v>
+        <v>2.012026740604361</v>
       </c>
       <c r="U62">
         <v>0.2008</v>
       </c>
       <c r="V62">
-        <v>0.1287951641709026</v>
+        <v>0.1266837680369534</v>
       </c>
       <c r="W62">
-        <v>0.1749379310344827</v>
+        <v>0.1753618993781798</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.5724229518706783</v>
+        <v>0.5630389690531261</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2373744429247516</v>
+        <v>0.2389244429247516</v>
       </c>
       <c r="C63">
-        <v>70.55550734445205</v>
+        <v>62.74909421277323</v>
       </c>
       <c r="D63">
-        <v>318.644507344452</v>
+        <v>316.0870942127733</v>
       </c>
       <c r="E63">
-        <v>71.98899999999998</v>
+        <v>77.238</v>
       </c>
       <c r="F63">
-        <v>320.189</v>
+        <v>325.438</v>
       </c>
       <c r="G63">
         <v>72.09999999999999</v>
@@ -6447,37 +6447,37 @@
         <v>36.2</v>
       </c>
       <c r="M63">
-        <v>64.2939512</v>
+        <v>65.3479504</v>
       </c>
       <c r="N63">
-        <v>-28.09395119999999</v>
+        <v>-29.1479504</v>
       </c>
       <c r="O63">
-        <v>-6.321139019999999</v>
+        <v>-6.55828884</v>
       </c>
       <c r="P63">
-        <v>-21.77281218</v>
+        <v>-22.58966156</v>
       </c>
       <c r="Q63">
-        <v>-8.372812179999995</v>
+        <v>-9.189661559999999</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.3343684212924665</v>
+        <v>0.3419623271159525</v>
       </c>
       <c r="T63">
-        <v>2.012026740604361</v>
+        <v>2.064974812725529</v>
       </c>
       <c r="U63">
         <v>0.2008</v>
       </c>
       <c r="V63">
-        <v>0.1266837680369534</v>
+        <v>0.1246404814557122</v>
       </c>
       <c r="W63">
-        <v>0.1753618993781798</v>
+        <v>0.175772191323693</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.5630389690531261</v>
+        <v>0.5539576953587209</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2389244429247516</v>
+        <v>0.2404744429247516</v>
       </c>
       <c r="C64">
-        <v>62.74909421277323</v>
+        <v>54.98340538259561</v>
       </c>
       <c r="D64">
-        <v>316.0870942127733</v>
+        <v>313.5704053825956</v>
       </c>
       <c r="E64">
-        <v>77.238</v>
+        <v>82.48700000000002</v>
       </c>
       <c r="F64">
-        <v>325.438</v>
+        <v>330.687</v>
       </c>
       <c r="G64">
         <v>72.09999999999999</v>
@@ -6529,37 +6529,37 @@
         <v>36.2</v>
       </c>
       <c r="M64">
-        <v>65.3479504</v>
+        <v>66.40194960000001</v>
       </c>
       <c r="N64">
-        <v>-29.1479504</v>
+        <v>-30.20194960000001</v>
       </c>
       <c r="O64">
-        <v>-6.55828884</v>
+        <v>-6.795438660000001</v>
       </c>
       <c r="P64">
-        <v>-22.58966156</v>
+        <v>-23.40651094</v>
       </c>
       <c r="Q64">
-        <v>-9.189661559999999</v>
+        <v>-10.00651094</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.3419623271159525</v>
+        <v>0.3499667143353025</v>
       </c>
       <c r="T64">
-        <v>2.064974812725529</v>
+        <v>2.120784942799192</v>
       </c>
       <c r="U64">
         <v>0.2008</v>
       </c>
       <c r="V64">
-        <v>0.1246404814557122</v>
+        <v>0.1226620611151453</v>
       </c>
       <c r="W64">
-        <v>0.175772191323693</v>
+        <v>0.1761694581280788</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.5539576953587209</v>
+        <v>0.5451647160673125</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2404744429247516</v>
+        <v>0.2420244429247516</v>
       </c>
       <c r="C65">
-        <v>54.98340538259561</v>
+        <v>47.25747579574778</v>
       </c>
       <c r="D65">
-        <v>313.5704053825956</v>
+        <v>311.0934757957478</v>
       </c>
       <c r="E65">
-        <v>82.48700000000002</v>
+        <v>87.73599999999999</v>
       </c>
       <c r="F65">
-        <v>330.687</v>
+        <v>335.936</v>
       </c>
       <c r="G65">
         <v>72.09999999999999</v>
@@ -6611,37 +6611,37 @@
         <v>36.2</v>
       </c>
       <c r="M65">
-        <v>66.40194960000001</v>
+        <v>67.4559488</v>
       </c>
       <c r="N65">
-        <v>-30.20194960000001</v>
+        <v>-31.2559488</v>
       </c>
       <c r="O65">
-        <v>-6.795438660000001</v>
+        <v>-7.03258848</v>
       </c>
       <c r="P65">
-        <v>-23.40651094</v>
+        <v>-24.22336032</v>
       </c>
       <c r="Q65">
-        <v>-10.00651094</v>
+        <v>-10.82336032</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.3499667143353025</v>
+        <v>0.3584157897335054</v>
       </c>
       <c r="T65">
-        <v>2.120784942799192</v>
+        <v>2.179695635654725</v>
       </c>
       <c r="U65">
         <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.1226620611151453</v>
+        <v>0.1207454664102212</v>
       </c>
       <c r="W65">
-        <v>0.1761694581280788</v>
+        <v>0.1765543103448276</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.5451647160673125</v>
+        <v>0.5366465173787609</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2420244429247516</v>
+        <v>0.2435744429247516</v>
       </c>
       <c r="C66">
-        <v>47.25747579574778</v>
+        <v>39.57037064751654</v>
       </c>
       <c r="D66">
-        <v>311.0934757957478</v>
+        <v>308.6553706475166</v>
       </c>
       <c r="E66">
-        <v>87.73599999999999</v>
+        <v>92.98500000000001</v>
       </c>
       <c r="F66">
-        <v>335.936</v>
+        <v>341.185</v>
       </c>
       <c r="G66">
         <v>72.09999999999999</v>
@@ -6693,37 +6693,37 @@
         <v>36.2</v>
       </c>
       <c r="M66">
-        <v>67.4559488</v>
+        <v>68.50994800000001</v>
       </c>
       <c r="N66">
-        <v>-31.2559488</v>
+        <v>-32.30994800000001</v>
       </c>
       <c r="O66">
-        <v>-7.03258848</v>
+        <v>-7.269738300000001</v>
       </c>
       <c r="P66">
-        <v>-24.22336032</v>
+        <v>-25.04020970000001</v>
       </c>
       <c r="Q66">
-        <v>-10.82336032</v>
+        <v>-11.64020970000001</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.3584157897335054</v>
+        <v>0.367347669440177</v>
       </c>
       <c r="T66">
-        <v>2.179695635654725</v>
+        <v>2.241972653816289</v>
       </c>
       <c r="U66">
         <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.1207454664102212</v>
+        <v>0.1188878438500639</v>
       </c>
       <c r="W66">
-        <v>0.1765543103448276</v>
+        <v>0.1769273209549072</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.5366465173787609</v>
+        <v>0.5283904171113952</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2435744429247516</v>
+        <v>0.2451244429247516</v>
       </c>
       <c r="C67">
-        <v>39.57037064751654</v>
+        <v>31.92118421035065</v>
       </c>
       <c r="D67">
-        <v>308.6553706475166</v>
+        <v>306.2551842103506</v>
       </c>
       <c r="E67">
-        <v>92.98500000000001</v>
+        <v>98.23400000000004</v>
       </c>
       <c r="F67">
-        <v>341.185</v>
+        <v>346.434</v>
       </c>
       <c r="G67">
         <v>72.09999999999999</v>
@@ -6775,37 +6775,37 @@
         <v>36.2</v>
       </c>
       <c r="M67">
-        <v>68.50994800000001</v>
+        <v>69.5639472</v>
       </c>
       <c r="N67">
-        <v>-32.30994800000001</v>
+        <v>-33.3639472</v>
       </c>
       <c r="O67">
-        <v>-7.269738300000001</v>
+        <v>-7.50688812</v>
       </c>
       <c r="P67">
-        <v>-25.04020970000001</v>
+        <v>-25.85705908</v>
       </c>
       <c r="Q67">
-        <v>-11.64020970000001</v>
+        <v>-12.45705908</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.367347669440177</v>
+        <v>0.3768049538354763</v>
       </c>
       <c r="T67">
-        <v>2.241972653816289</v>
+        <v>2.307913025987356</v>
       </c>
       <c r="U67">
         <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.1188878438500639</v>
+        <v>0.1170865128826387</v>
       </c>
       <c r="W67">
-        <v>0.1769273209549072</v>
+        <v>0.1772890282131661</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.5283904171113952</v>
+        <v>0.5203845017006166</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2451244429247516</v>
+        <v>0.2466744429247516</v>
       </c>
       <c r="C68">
-        <v>31.92118421035065</v>
+        <v>24.30903871202622</v>
       </c>
       <c r="D68">
-        <v>306.2551842103506</v>
+        <v>303.8920387120262</v>
       </c>
       <c r="E68">
-        <v>98.23400000000004</v>
+        <v>103.483</v>
       </c>
       <c r="F68">
-        <v>346.434</v>
+        <v>351.683</v>
       </c>
       <c r="G68">
         <v>72.09999999999999</v>
@@ -6857,37 +6857,37 @@
         <v>36.2</v>
       </c>
       <c r="M68">
-        <v>69.5639472</v>
+        <v>70.61794639999999</v>
       </c>
       <c r="N68">
-        <v>-33.3639472</v>
+        <v>-34.41794639999999</v>
       </c>
       <c r="O68">
-        <v>-7.50688812</v>
+        <v>-7.744037939999998</v>
       </c>
       <c r="P68">
-        <v>-25.85705908</v>
+        <v>-26.67390845999999</v>
       </c>
       <c r="Q68">
-        <v>-12.45705908</v>
+        <v>-13.27390845999999</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.3768049538354763</v>
+        <v>0.3868354069820059</v>
       </c>
       <c r="T68">
-        <v>2.307913025987356</v>
+        <v>2.377849784350609</v>
       </c>
       <c r="U68">
         <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.1170865128826387</v>
+        <v>0.115338952988868</v>
       </c>
       <c r="W68">
-        <v>0.1772890282131661</v>
+        <v>0.1776399382398353</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.5203845017006166</v>
+        <v>0.5126175688394135</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2466744429247516</v>
+        <v>0.2482244429247516</v>
       </c>
       <c r="C69">
-        <v>24.30903871202622</v>
+        <v>16.73308326535255</v>
       </c>
       <c r="D69">
-        <v>303.8920387120262</v>
+        <v>301.5650832653525</v>
       </c>
       <c r="E69">
-        <v>103.483</v>
+        <v>108.732</v>
       </c>
       <c r="F69">
-        <v>351.683</v>
+        <v>356.932</v>
       </c>
       <c r="G69">
         <v>72.09999999999999</v>
@@ -6939,37 +6939,37 @@
         <v>36.2</v>
       </c>
       <c r="M69">
-        <v>70.61794639999999</v>
+        <v>71.6719456</v>
       </c>
       <c r="N69">
-        <v>-34.41794639999999</v>
+        <v>-35.4719456</v>
       </c>
       <c r="O69">
-        <v>-7.744037939999998</v>
+        <v>-7.98118776</v>
       </c>
       <c r="P69">
-        <v>-26.67390845999999</v>
+        <v>-27.49075784</v>
       </c>
       <c r="Q69">
-        <v>-13.27390845999999</v>
+        <v>-14.09075784</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.3868354069820059</v>
+        <v>0.3974927634501936</v>
       </c>
       <c r="T69">
-        <v>2.377849784350609</v>
+        <v>2.452157590111566</v>
       </c>
       <c r="U69">
         <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.115338952988868</v>
+        <v>0.1136427919155023</v>
       </c>
       <c r="W69">
-        <v>0.1776399382398353</v>
+        <v>0.1779805273833671</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.5126175688394135</v>
+        <v>0.5050790751800103</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2482244429247516</v>
+        <v>0.2753234411444437</v>
       </c>
       <c r="C70">
-        <v>16.73308326535255</v>
+        <v>-24.12060971842959</v>
       </c>
       <c r="D70">
-        <v>301.5650832653525</v>
+        <v>265.9603902815705</v>
       </c>
       <c r="E70">
-        <v>108.732</v>
+        <v>113.9810000000001</v>
       </c>
       <c r="F70">
-        <v>356.932</v>
+        <v>362.181</v>
       </c>
       <c r="G70">
         <v>72.09999999999999</v>
@@ -7021,45 +7021,45 @@
         <v>36.2</v>
       </c>
       <c r="M70">
-        <v>71.6719456</v>
+        <v>85.40227980000002</v>
       </c>
       <c r="N70">
-        <v>-35.4719456</v>
+        <v>-49.20227980000001</v>
       </c>
       <c r="O70">
-        <v>-7.98118776</v>
+        <v>-11.070512955</v>
       </c>
       <c r="P70">
-        <v>-27.49075784</v>
+        <v>-38.13176684500001</v>
       </c>
       <c r="Q70">
-        <v>-14.09075784</v>
+        <v>-24.73176684500001</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.3974927634501936</v>
+        <v>0.4133505887863037</v>
       </c>
       <c r="T70">
-        <v>2.452157590111566</v>
+        <v>2.562725366312377</v>
       </c>
       <c r="U70">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.1136427919155023</v>
+        <v>0.09537216124762046</v>
       </c>
       <c r="W70">
-        <v>0.1779805273833671</v>
+        <v>0.2133112443778111</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y70">
-        <v>0.5050790751800103</v>
+        <v>0.4238762722116465</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2753234411444437</v>
+        <v>0.2772234411444437</v>
       </c>
       <c r="C71">
-        <v>-24.12060971842959</v>
+        <v>-31.55316009273923</v>
       </c>
       <c r="D71">
-        <v>265.9603902815705</v>
+        <v>263.7768399072608</v>
       </c>
       <c r="E71">
-        <v>113.9810000000001</v>
+        <v>119.23</v>
       </c>
       <c r="F71">
-        <v>362.181</v>
+        <v>367.43</v>
       </c>
       <c r="G71">
         <v>72.09999999999999</v>
@@ -7103,37 +7103,37 @@
         <v>36.2</v>
       </c>
       <c r="M71">
-        <v>85.40227980000002</v>
+        <v>86.639994</v>
       </c>
       <c r="N71">
-        <v>-49.20227980000001</v>
+        <v>-50.439994</v>
       </c>
       <c r="O71">
-        <v>-11.070512955</v>
+        <v>-11.34899865</v>
       </c>
       <c r="P71">
-        <v>-38.13176684500001</v>
+        <v>-39.09099535</v>
       </c>
       <c r="Q71">
-        <v>-24.73176684500001</v>
+        <v>-25.69099535</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.4133505887863037</v>
+        <v>0.4256022750791804</v>
       </c>
       <c r="T71">
-        <v>2.562725366312377</v>
+        <v>2.648149545189456</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.09537216124762046</v>
+        <v>0.09400970180122591</v>
       </c>
       <c r="W71">
-        <v>0.2133112443778111</v>
+        <v>0.2136325123152709</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.4238762722116465</v>
+        <v>0.4178208968943373</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2772234411444437</v>
+        <v>0.2791234411444438</v>
       </c>
       <c r="C72">
-        <v>-31.55316009273923</v>
+        <v>-38.95014828186225</v>
       </c>
       <c r="D72">
-        <v>263.7768399072608</v>
+        <v>261.6288517181378</v>
       </c>
       <c r="E72">
-        <v>119.23</v>
+        <v>124.479</v>
       </c>
       <c r="F72">
-        <v>367.43</v>
+        <v>372.679</v>
       </c>
       <c r="G72">
         <v>72.09999999999999</v>
@@ -7185,37 +7185,37 @@
         <v>36.2</v>
       </c>
       <c r="M72">
-        <v>86.639994</v>
+        <v>87.87770820000001</v>
       </c>
       <c r="N72">
-        <v>-50.439994</v>
+        <v>-51.67770820000001</v>
       </c>
       <c r="O72">
-        <v>-11.34899865</v>
+        <v>-11.627484345</v>
       </c>
       <c r="P72">
-        <v>-39.09099535</v>
+        <v>-40.05022385500001</v>
       </c>
       <c r="Q72">
-        <v>-25.69099535</v>
+        <v>-26.65022385500001</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.4256022750791804</v>
+        <v>0.4386989052543246</v>
       </c>
       <c r="T72">
-        <v>2.648149545189456</v>
+        <v>2.739465046747713</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.09400970180122591</v>
+        <v>0.09268562149416637</v>
       </c>
       <c r="W72">
-        <v>0.2136325123152709</v>
+        <v>0.2139447304516756</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.4178208968943373</v>
+        <v>0.4119360955296283</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2791234411444438</v>
+        <v>0.2810234411444438</v>
       </c>
       <c r="C73">
-        <v>-38.9501482818622</v>
+        <v>-46.31243603858377</v>
       </c>
       <c r="D73">
-        <v>261.6288517181378</v>
+        <v>259.5155639614162</v>
       </c>
       <c r="E73">
-        <v>124.479</v>
+        <v>129.728</v>
       </c>
       <c r="F73">
-        <v>372.679</v>
+        <v>377.928</v>
       </c>
       <c r="G73">
         <v>72.09999999999999</v>
@@ -7267,37 +7267,37 @@
         <v>36.2</v>
       </c>
       <c r="M73">
-        <v>87.8777082</v>
+        <v>89.1154224</v>
       </c>
       <c r="N73">
-        <v>-51.6777082</v>
+        <v>-52.9154224</v>
       </c>
       <c r="O73">
-        <v>-11.627484345</v>
+        <v>-11.90597004</v>
       </c>
       <c r="P73">
-        <v>-40.050223855</v>
+        <v>-41.00945236</v>
       </c>
       <c r="Q73">
-        <v>-26.650223855</v>
+        <v>-27.60945236</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.4386989052543245</v>
+        <v>0.4527310090134075</v>
       </c>
       <c r="T73">
-        <v>2.739465046747712</v>
+        <v>2.837303084131559</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.09268562149416638</v>
+        <v>0.09139832119563629</v>
       </c>
       <c r="W73">
-        <v>0.2139447304516756</v>
+        <v>0.214248275862069</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.4119360955296283</v>
+        <v>0.4062147608694946</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2810234411444438</v>
+        <v>0.2829234411444437</v>
       </c>
       <c r="C74">
-        <v>-46.31243603858377</v>
+        <v>-53.64085749580835</v>
       </c>
       <c r="D74">
-        <v>259.5155639614162</v>
+        <v>257.4361425041917</v>
       </c>
       <c r="E74">
-        <v>129.728</v>
+        <v>134.977</v>
       </c>
       <c r="F74">
-        <v>377.928</v>
+        <v>383.177</v>
       </c>
       <c r="G74">
         <v>72.09999999999999</v>
@@ -7349,37 +7349,37 @@
         <v>36.2</v>
       </c>
       <c r="M74">
-        <v>89.1154224</v>
+        <v>90.3531366</v>
       </c>
       <c r="N74">
-        <v>-52.9154224</v>
+        <v>-54.1531366</v>
       </c>
       <c r="O74">
-        <v>-11.90597004</v>
+        <v>-12.184455735</v>
       </c>
       <c r="P74">
-        <v>-41.00945236</v>
+        <v>-41.968680865</v>
       </c>
       <c r="Q74">
-        <v>-27.60945236</v>
+        <v>-28.568680865</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.4527310090134075</v>
+        <v>0.4678025278657559</v>
       </c>
       <c r="T74">
-        <v>2.837303084131559</v>
+        <v>2.942388383543839</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.09139832119563629</v>
+        <v>0.09014628939843579</v>
       </c>
       <c r="W74">
-        <v>0.214248275862069</v>
+        <v>0.2145435049598488</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.4062147608694946</v>
+        <v>0.400650175104159</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2829234411444437</v>
+        <v>0.2848234411444437</v>
       </c>
       <c r="C75">
-        <v>-53.64085749580835</v>
+        <v>-60.93622026431348</v>
       </c>
       <c r="D75">
-        <v>257.4361425041917</v>
+        <v>255.3897797356865</v>
       </c>
       <c r="E75">
-        <v>134.977</v>
+        <v>140.226</v>
       </c>
       <c r="F75">
-        <v>383.177</v>
+        <v>388.426</v>
       </c>
       <c r="G75">
         <v>72.09999999999999</v>
@@ -7431,37 +7431,37 @@
         <v>36.2</v>
       </c>
       <c r="M75">
-        <v>90.3531366</v>
+        <v>91.5908508</v>
       </c>
       <c r="N75">
-        <v>-54.1531366</v>
+        <v>-55.3908508</v>
       </c>
       <c r="O75">
-        <v>-12.184455735</v>
+        <v>-12.46294143</v>
       </c>
       <c r="P75">
-        <v>-41.968680865</v>
+        <v>-42.92790936999999</v>
       </c>
       <c r="Q75">
-        <v>-28.568680865</v>
+        <v>-29.52790937</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.4678025278657559</v>
+        <v>0.4840333943221311</v>
       </c>
       <c r="T75">
-        <v>2.942388383543839</v>
+        <v>3.055557167526294</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.09014628939843579</v>
+        <v>0.08892809629845692</v>
       </c>
       <c r="W75">
-        <v>0.2145435049598488</v>
+        <v>0.2148307548928239</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.400650175104159</v>
+        <v>0.3952359835486975</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2848234411444437</v>
+        <v>0.2867234411444438</v>
       </c>
       <c r="C76">
-        <v>-60.93622026431348</v>
+        <v>-68.19930647855983</v>
       </c>
       <c r="D76">
-        <v>255.3897797356865</v>
+        <v>253.3756935214401</v>
       </c>
       <c r="E76">
-        <v>140.226</v>
+        <v>145.475</v>
       </c>
       <c r="F76">
-        <v>388.426</v>
+        <v>393.675</v>
       </c>
       <c r="G76">
         <v>72.09999999999999</v>
@@ -7513,37 +7513,37 @@
         <v>36.2</v>
       </c>
       <c r="M76">
-        <v>91.5908508</v>
+        <v>92.828565</v>
       </c>
       <c r="N76">
-        <v>-55.3908508</v>
+        <v>-56.62856499999999</v>
       </c>
       <c r="O76">
-        <v>-12.46294143</v>
+        <v>-12.741427125</v>
       </c>
       <c r="P76">
-        <v>-42.92790936999999</v>
+        <v>-43.88713787499999</v>
       </c>
       <c r="Q76">
-        <v>-29.52790937</v>
+        <v>-30.48713787499999</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.4840333943221311</v>
+        <v>0.5015627300950164</v>
       </c>
       <c r="T76">
-        <v>3.055557167526294</v>
+        <v>3.177779454227347</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.08892809629845692</v>
+        <v>0.08774238834781084</v>
       </c>
       <c r="W76">
-        <v>0.2148307548928239</v>
+        <v>0.2151103448275862</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3952359835486975</v>
+        <v>0.3899661704347148</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2867234411444438</v>
+        <v>0.2886234411444437</v>
       </c>
       <c r="C77">
-        <v>-68.19930647855983</v>
+        <v>-75.43087379340295</v>
       </c>
       <c r="D77">
-        <v>253.3756935214401</v>
+        <v>251.393126206597</v>
       </c>
       <c r="E77">
-        <v>145.475</v>
+        <v>150.724</v>
       </c>
       <c r="F77">
-        <v>393.675</v>
+        <v>398.924</v>
       </c>
       <c r="G77">
         <v>72.09999999999999</v>
@@ -7595,37 +7595,37 @@
         <v>36.2</v>
       </c>
       <c r="M77">
-        <v>92.828565</v>
+        <v>94.0662792</v>
       </c>
       <c r="N77">
-        <v>-56.62856499999999</v>
+        <v>-57.86627919999999</v>
       </c>
       <c r="O77">
-        <v>-12.741427125</v>
+        <v>-13.01991282</v>
       </c>
       <c r="P77">
-        <v>-43.88713787499999</v>
+        <v>-44.84636637999999</v>
       </c>
       <c r="Q77">
-        <v>-30.48713787499999</v>
+        <v>-31.44636637999999</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.5015627300950164</v>
+        <v>0.5205528438489754</v>
       </c>
       <c r="T77">
-        <v>3.177779454227347</v>
+        <v>3.31018693148682</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.08774238834781084</v>
+        <v>0.08658788323797123</v>
       </c>
       <c r="W77">
-        <v>0.2151103448275862</v>
+        <v>0.2153825771324864</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3899661704347148</v>
+        <v>0.3848350366132054</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2886234411444437</v>
+        <v>0.2905234411444438</v>
       </c>
       <c r="C78">
-        <v>-75.43087379340295</v>
+        <v>-82.63165633437598</v>
       </c>
       <c r="D78">
-        <v>251.393126206597</v>
+        <v>249.4413436656241</v>
       </c>
       <c r="E78">
-        <v>150.724</v>
+        <v>155.973</v>
       </c>
       <c r="F78">
-        <v>398.924</v>
+        <v>404.173</v>
       </c>
       <c r="G78">
         <v>72.09999999999999</v>
@@ -7677,37 +7677,37 @@
         <v>36.2</v>
       </c>
       <c r="M78">
-        <v>94.0662792</v>
+        <v>95.30399340000001</v>
       </c>
       <c r="N78">
-        <v>-57.86627919999999</v>
+        <v>-59.10399340000001</v>
       </c>
       <c r="O78">
-        <v>-13.01991282</v>
+        <v>-13.298398515</v>
       </c>
       <c r="P78">
-        <v>-44.84636637999999</v>
+        <v>-45.805594885</v>
       </c>
       <c r="Q78">
-        <v>-31.44636637999999</v>
+        <v>-32.40559488500001</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.5205528438489754</v>
+        <v>0.5411942718424092</v>
       </c>
       <c r="T78">
-        <v>3.31018693148682</v>
+        <v>3.454108102421029</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.08658788323797123</v>
+        <v>0.08546336527384171</v>
       </c>
       <c r="W78">
-        <v>0.2153825771324864</v>
+        <v>0.2156477384684281</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3848350366132054</v>
+        <v>0.379837178994852</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2905234411444438</v>
+        <v>0.2924234411444437</v>
       </c>
       <c r="C79">
-        <v>-82.63165633437598</v>
+        <v>-89.80236560404381</v>
       </c>
       <c r="D79">
-        <v>249.4413436656241</v>
+        <v>247.5196343959561</v>
       </c>
       <c r="E79">
-        <v>155.973</v>
+        <v>161.222</v>
       </c>
       <c r="F79">
-        <v>404.173</v>
+        <v>409.422</v>
       </c>
       <c r="G79">
         <v>72.09999999999999</v>
@@ -7759,37 +7759,37 @@
         <v>36.2</v>
       </c>
       <c r="M79">
-        <v>95.30399340000001</v>
+        <v>96.5417076</v>
       </c>
       <c r="N79">
-        <v>-59.10399340000001</v>
+        <v>-60.34170759999999</v>
       </c>
       <c r="O79">
-        <v>-13.298398515</v>
+        <v>-13.57688421</v>
       </c>
       <c r="P79">
-        <v>-45.805594885</v>
+        <v>-46.76482338999999</v>
       </c>
       <c r="Q79">
-        <v>-32.40559488500001</v>
+        <v>-33.36482338999999</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.5411942718424092</v>
+        <v>0.5637121932897914</v>
       </c>
       <c r="T79">
-        <v>3.454108102421029</v>
+        <v>3.61111301616744</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.08546336527384171</v>
+        <v>0.08436768110366427</v>
       </c>
       <c r="W79">
-        <v>0.2156477384684281</v>
+        <v>0.215906100795756</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.379837178994852</v>
+        <v>0.3749674715718412</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2924234411444437</v>
+        <v>0.2943234411444438</v>
       </c>
       <c r="C80">
-        <v>-89.80236560404381</v>
+        <v>-96.94369134678533</v>
       </c>
       <c r="D80">
-        <v>247.5196343959561</v>
+        <v>245.6273086532147</v>
       </c>
       <c r="E80">
-        <v>161.222</v>
+        <v>166.471</v>
       </c>
       <c r="F80">
-        <v>409.422</v>
+        <v>414.671</v>
       </c>
       <c r="G80">
         <v>72.09999999999999</v>
@@ -7841,37 +7841,37 @@
         <v>36.2</v>
       </c>
       <c r="M80">
-        <v>96.5417076</v>
+        <v>97.77942180000001</v>
       </c>
       <c r="N80">
-        <v>-60.34170759999999</v>
+        <v>-61.57942180000001</v>
       </c>
       <c r="O80">
-        <v>-13.57688421</v>
+        <v>-13.855369905</v>
       </c>
       <c r="P80">
-        <v>-46.76482338999999</v>
+        <v>-47.724051895</v>
       </c>
       <c r="Q80">
-        <v>-33.36482338999999</v>
+        <v>-34.324051895</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.5637121932897914</v>
+        <v>0.5883746786845433</v>
       </c>
       <c r="T80">
-        <v>3.61111301616744</v>
+        <v>3.78307077884208</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.08436768110366427</v>
+        <v>0.08329973577323814</v>
       </c>
       <c r="W80">
-        <v>0.215906100795756</v>
+        <v>0.2161579223046705</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3749674715718412</v>
+        <v>0.3702210478810584</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2943234411444438</v>
+        <v>0.2962234411444438</v>
       </c>
       <c r="C81">
-        <v>-96.94369134678533</v>
+        <v>-104.0563023742048</v>
       </c>
       <c r="D81">
-        <v>245.6273086532147</v>
+        <v>243.7636976257952</v>
       </c>
       <c r="E81">
-        <v>166.471</v>
+        <v>171.72</v>
       </c>
       <c r="F81">
-        <v>414.671</v>
+        <v>419.92</v>
       </c>
       <c r="G81">
         <v>72.09999999999999</v>
@@ -7923,37 +7923,37 @@
         <v>36.2</v>
       </c>
       <c r="M81">
-        <v>97.77942180000001</v>
+        <v>99.01713600000001</v>
       </c>
       <c r="N81">
-        <v>-61.57942180000001</v>
+        <v>-62.817136</v>
       </c>
       <c r="O81">
-        <v>-13.855369905</v>
+        <v>-14.1338556</v>
       </c>
       <c r="P81">
-        <v>-47.724051895</v>
+        <v>-48.6832804</v>
       </c>
       <c r="Q81">
-        <v>-34.324051895</v>
+        <v>-35.2832804</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.5883746786845433</v>
+        <v>0.6155034126187705</v>
       </c>
       <c r="T81">
-        <v>3.78307077884208</v>
+        <v>3.972224317784184</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.08329973577323814</v>
+        <v>0.08225848907607265</v>
       </c>
       <c r="W81">
-        <v>0.2161579223046705</v>
+        <v>0.2164034482758621</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3702210478810584</v>
+        <v>0.3655932847825452</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2962234411444438</v>
+        <v>0.2981234411444438</v>
       </c>
       <c r="C82">
-        <v>-104.0563023742048</v>
+        <v>-111.1408473532535</v>
       </c>
       <c r="D82">
-        <v>243.7636976257952</v>
+        <v>241.9281526467464</v>
       </c>
       <c r="E82">
-        <v>171.72</v>
+        <v>176.969</v>
       </c>
       <c r="F82">
-        <v>419.92</v>
+        <v>425.169</v>
       </c>
       <c r="G82">
         <v>72.09999999999999</v>
@@ -8005,37 +8005,37 @@
         <v>36.2</v>
       </c>
       <c r="M82">
-        <v>99.01713600000001</v>
+        <v>100.2548502</v>
       </c>
       <c r="N82">
-        <v>-62.817136</v>
+        <v>-64.0548502</v>
       </c>
       <c r="O82">
-        <v>-14.1338556</v>
+        <v>-14.412341295</v>
       </c>
       <c r="P82">
-        <v>-48.6832804</v>
+        <v>-49.642508905</v>
       </c>
       <c r="Q82">
-        <v>-35.2832804</v>
+        <v>-36.242508905</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.6155034126187705</v>
+        <v>0.6454878027566007</v>
       </c>
       <c r="T82">
-        <v>3.972224317784184</v>
+        <v>4.181288755562299</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.08225848907607265</v>
+        <v>0.08124295217389892</v>
       </c>
       <c r="W82">
-        <v>0.2164034482758621</v>
+        <v>0.2166429118773947</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3655932847825452</v>
+        <v>0.3610797874395507</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2981234411444438</v>
+        <v>0.3000234411444438</v>
       </c>
       <c r="C83">
-        <v>-111.1408473532535</v>
+        <v>-118.1979555590098</v>
       </c>
       <c r="D83">
-        <v>241.9281526467464</v>
+        <v>240.1200444409903</v>
       </c>
       <c r="E83">
-        <v>176.969</v>
+        <v>182.218</v>
       </c>
       <c r="F83">
-        <v>425.169</v>
+        <v>430.418</v>
       </c>
       <c r="G83">
         <v>72.09999999999999</v>
@@ -8087,37 +8087,37 @@
         <v>36.2</v>
       </c>
       <c r="M83">
-        <v>100.2548502</v>
+        <v>101.4925644</v>
       </c>
       <c r="N83">
-        <v>-64.0548502</v>
+        <v>-65.2925644</v>
       </c>
       <c r="O83">
-        <v>-14.412341295</v>
+        <v>-14.69082699</v>
       </c>
       <c r="P83">
-        <v>-49.642508905</v>
+        <v>-50.60173741</v>
       </c>
       <c r="Q83">
-        <v>-36.242508905</v>
+        <v>-37.20173741</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.6454878027566007</v>
+        <v>0.678803791798634</v>
       </c>
       <c r="T83">
-        <v>4.181288755562299</v>
+        <v>4.41358257531576</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.08124295217389892</v>
+        <v>0.08025218446446113</v>
       </c>
       <c r="W83">
-        <v>0.2166429118773947</v>
+        <v>0.2168765349032801</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3610797874395507</v>
+        <v>0.356676375397605</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.3000234411444438</v>
+        <v>0.3019234411444437</v>
       </c>
       <c r="C84">
-        <v>-118.1979555590098</v>
+        <v>-125.2282375939508</v>
       </c>
       <c r="D84">
-        <v>240.1200444409903</v>
+        <v>238.3387624060492</v>
       </c>
       <c r="E84">
-        <v>182.218</v>
+        <v>187.467</v>
       </c>
       <c r="F84">
-        <v>430.418</v>
+        <v>435.667</v>
       </c>
       <c r="G84">
         <v>72.09999999999999</v>
@@ -8169,37 +8169,37 @@
         <v>36.2</v>
       </c>
       <c r="M84">
-        <v>101.4925644</v>
+        <v>102.7302786</v>
       </c>
       <c r="N84">
-        <v>-65.2925644</v>
+        <v>-66.5302786</v>
       </c>
       <c r="O84">
-        <v>-14.69082699</v>
+        <v>-14.969312685</v>
       </c>
       <c r="P84">
-        <v>-50.60173741</v>
+        <v>-51.560965915</v>
       </c>
       <c r="Q84">
-        <v>-37.20173741</v>
+        <v>-38.16096591500001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.678803791798634</v>
+        <v>0.7160393089632596</v>
       </c>
       <c r="T84">
-        <v>4.41358257531576</v>
+        <v>4.6732050797461</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.08025218446446113</v>
+        <v>0.07928529067573267</v>
       </c>
       <c r="W84">
-        <v>0.2168765349032801</v>
+        <v>0.2171045284586622</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.356676375397605</v>
+        <v>0.3523790696699231</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.3019234411444437</v>
+        <v>0.3038234411444438</v>
       </c>
       <c r="C85">
-        <v>-125.2282375939508</v>
+        <v>-132.2322860754489</v>
       </c>
       <c r="D85">
-        <v>238.3387624060492</v>
+        <v>236.5837139245511</v>
       </c>
       <c r="E85">
-        <v>187.467</v>
+        <v>192.716</v>
       </c>
       <c r="F85">
-        <v>435.667</v>
+        <v>440.916</v>
       </c>
       <c r="G85">
         <v>72.09999999999999</v>
@@ -8251,37 +8251,37 @@
         <v>36.2</v>
       </c>
       <c r="M85">
-        <v>102.7302786</v>
+        <v>103.9679928</v>
       </c>
       <c r="N85">
-        <v>-66.5302786</v>
+        <v>-67.7679928</v>
       </c>
       <c r="O85">
-        <v>-14.969312685</v>
+        <v>-15.24779838</v>
       </c>
       <c r="P85">
-        <v>-51.560965915</v>
+        <v>-52.52019442</v>
       </c>
       <c r="Q85">
-        <v>-38.16096591500001</v>
+        <v>-39.12019442</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.7160393089632596</v>
+        <v>0.7579292657734634</v>
       </c>
       <c r="T85">
-        <v>4.6732050797461</v>
+        <v>4.965280397230232</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.07928529067573267</v>
+        <v>0.07834141816768825</v>
       </c>
       <c r="W85">
-        <v>0.2171045284586622</v>
+        <v>0.2173270935960591</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3523790696699231</v>
+        <v>0.3481840807452811</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.3038234411444438</v>
+        <v>0.3057234411444437</v>
       </c>
       <c r="C86">
-        <v>-132.2322860754489</v>
+        <v>-139.2106762931124</v>
       </c>
       <c r="D86">
-        <v>236.5837139245511</v>
+        <v>234.8543237068876</v>
       </c>
       <c r="E86">
-        <v>192.716</v>
+        <v>197.965</v>
       </c>
       <c r="F86">
-        <v>440.9159999999999</v>
+        <v>446.165</v>
       </c>
       <c r="G86">
         <v>72.09999999999999</v>
@@ -8333,37 +8333,37 @@
         <v>36.2</v>
       </c>
       <c r="M86">
-        <v>103.9679928</v>
+        <v>105.205707</v>
       </c>
       <c r="N86">
-        <v>-67.76799279999999</v>
+        <v>-69.00570699999999</v>
       </c>
       <c r="O86">
-        <v>-15.24779838</v>
+        <v>-15.526284075</v>
       </c>
       <c r="P86">
-        <v>-52.52019441999999</v>
+        <v>-53.47942292499999</v>
       </c>
       <c r="Q86">
-        <v>-39.12019441999999</v>
+        <v>-40.07942292499999</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.757929265773463</v>
+        <v>0.8054045501583605</v>
       </c>
       <c r="T86">
-        <v>4.965280397230228</v>
+        <v>5.29629909037891</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.07834141816768825</v>
+        <v>0.07741975442453898</v>
       </c>
       <c r="W86">
-        <v>0.2173270935960591</v>
+        <v>0.2175444219066937</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3481840807452811</v>
+        <v>0.3440877974423955</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.3057234411444437</v>
+        <v>0.3076234411444438</v>
       </c>
       <c r="C87">
-        <v>-139.2106762931124</v>
+        <v>-146.1639668375062</v>
       </c>
       <c r="D87">
-        <v>234.8543237068876</v>
+        <v>233.1500331624938</v>
       </c>
       <c r="E87">
-        <v>197.965</v>
+        <v>203.214</v>
       </c>
       <c r="F87">
-        <v>446.165</v>
+        <v>451.414</v>
       </c>
       <c r="G87">
         <v>72.09999999999999</v>
@@ -8415,37 +8415,37 @@
         <v>36.2</v>
       </c>
       <c r="M87">
-        <v>105.205707</v>
+        <v>106.4434212</v>
       </c>
       <c r="N87">
-        <v>-69.00570699999999</v>
+        <v>-70.2434212</v>
       </c>
       <c r="O87">
-        <v>-15.526284075</v>
+        <v>-15.80476977</v>
       </c>
       <c r="P87">
-        <v>-53.47942292499999</v>
+        <v>-54.43865143</v>
       </c>
       <c r="Q87">
-        <v>-40.07942292499999</v>
+        <v>-41.03865143</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.8054045501583605</v>
+        <v>0.859662018026815</v>
       </c>
       <c r="T87">
-        <v>5.29629909037891</v>
+        <v>5.674606168263119</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.07741975442453898</v>
+        <v>0.07651952472192805</v>
       </c>
       <c r="W87">
-        <v>0.2175444219066937</v>
+        <v>0.2177566960705694</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3440877974423955</v>
+        <v>0.3400867765419024</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.3076234411444438</v>
+        <v>0.3095234411444437</v>
       </c>
       <c r="C88">
-        <v>-146.1639668375062</v>
+        <v>-153.0927002016939</v>
       </c>
       <c r="D88">
-        <v>233.1500331624938</v>
+        <v>231.4702997983061</v>
       </c>
       <c r="E88">
-        <v>203.214</v>
+        <v>208.463</v>
       </c>
       <c r="F88">
-        <v>451.414</v>
+        <v>456.663</v>
       </c>
       <c r="G88">
         <v>72.09999999999999</v>
@@ -8497,37 +8497,37 @@
         <v>36.2</v>
       </c>
       <c r="M88">
-        <v>106.4434212</v>
+        <v>107.6811354</v>
       </c>
       <c r="N88">
-        <v>-70.2434212</v>
+        <v>-71.48113539999999</v>
       </c>
       <c r="O88">
-        <v>-15.80476977</v>
+        <v>-16.083255465</v>
       </c>
       <c r="P88">
-        <v>-54.43865143</v>
+        <v>-55.39787993499999</v>
       </c>
       <c r="Q88">
-        <v>-41.03865143</v>
+        <v>-41.99787993499999</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.859662018026815</v>
+        <v>0.9222667886442621</v>
       </c>
       <c r="T88">
-        <v>5.674606168263119</v>
+        <v>6.111114335052589</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.07651952472192805</v>
+        <v>0.07563998995500935</v>
       </c>
       <c r="W88">
-        <v>0.2177566960705694</v>
+        <v>0.2179640903686088</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3400867765419024</v>
+        <v>0.3361777331333748</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.3095234411444437</v>
+        <v>0.3114234411444438</v>
       </c>
       <c r="C89">
-        <v>-153.0927002016939</v>
+        <v>-159.9974033569649</v>
       </c>
       <c r="D89">
-        <v>231.4702997983061</v>
+        <v>229.8145966430351</v>
       </c>
       <c r="E89">
-        <v>208.463</v>
+        <v>213.712</v>
       </c>
       <c r="F89">
-        <v>456.663</v>
+        <v>461.912</v>
       </c>
       <c r="G89">
         <v>72.09999999999999</v>
@@ -8579,37 +8579,37 @@
         <v>36.2</v>
       </c>
       <c r="M89">
-        <v>107.6811354</v>
+        <v>108.9188496</v>
       </c>
       <c r="N89">
-        <v>-71.48113539999999</v>
+        <v>-72.7188496</v>
       </c>
       <c r="O89">
-        <v>-16.083255465</v>
+        <v>-16.36174116</v>
       </c>
       <c r="P89">
-        <v>-55.39787993499999</v>
+        <v>-56.35710844</v>
       </c>
       <c r="Q89">
-        <v>-41.99787993499999</v>
+        <v>-42.95710844</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.9222667886442621</v>
+        <v>0.9953056876979508</v>
       </c>
       <c r="T89">
-        <v>6.111114335052589</v>
+        <v>6.620373862973639</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.07563998995500935</v>
+        <v>0.0747804446146115</v>
       </c>
       <c r="W89">
-        <v>0.2179640903686088</v>
+        <v>0.2181667711598746</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3361777331333748</v>
+        <v>0.3323575316204955</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.3114234411444438</v>
+        <v>0.3133234411444438</v>
       </c>
       <c r="C90">
-        <v>-159.9974033569649</v>
+        <v>-166.8785883040253</v>
       </c>
       <c r="D90">
-        <v>229.8145966430351</v>
+        <v>228.1824116959747</v>
       </c>
       <c r="E90">
-        <v>213.712</v>
+        <v>218.961</v>
       </c>
       <c r="F90">
-        <v>461.912</v>
+        <v>467.161</v>
       </c>
       <c r="G90">
         <v>72.09999999999999</v>
@@ -8661,37 +8661,37 @@
         <v>36.2</v>
       </c>
       <c r="M90">
-        <v>108.9188496</v>
+        <v>110.1565638</v>
       </c>
       <c r="N90">
-        <v>-72.7188496</v>
+        <v>-73.9565638</v>
       </c>
       <c r="O90">
-        <v>-16.36174116</v>
+        <v>-16.640226855</v>
       </c>
       <c r="P90">
-        <v>-56.35710844</v>
+        <v>-57.316336945</v>
       </c>
       <c r="Q90">
-        <v>-42.95710844</v>
+        <v>-43.916336945</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.9953056876979508</v>
+        <v>1.081624386579583</v>
       </c>
       <c r="T90">
-        <v>6.620373862973639</v>
+        <v>7.222226032334878</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.0747804446146115</v>
+        <v>0.0739402148998406</v>
       </c>
       <c r="W90">
-        <v>0.2181667711598746</v>
+        <v>0.2183648973266176</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3323575316204955</v>
+        <v>0.3286231773326248</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.3133234411444438</v>
+        <v>0.3152234411444438</v>
       </c>
       <c r="C91">
-        <v>-166.8785883040253</v>
+        <v>-173.7367526008688</v>
       </c>
       <c r="D91">
-        <v>228.1824116959747</v>
+        <v>226.5732473991312</v>
       </c>
       <c r="E91">
-        <v>218.961</v>
+        <v>224.21</v>
       </c>
       <c r="F91">
-        <v>467.161</v>
+        <v>472.41</v>
       </c>
       <c r="G91">
         <v>72.09999999999999</v>
@@ -8743,37 +8743,37 @@
         <v>36.2</v>
       </c>
       <c r="M91">
-        <v>110.1565638</v>
+        <v>111.394278</v>
       </c>
       <c r="N91">
-        <v>-73.9565638</v>
+        <v>-75.194278</v>
       </c>
       <c r="O91">
-        <v>-16.640226855</v>
+        <v>-16.91871255</v>
       </c>
       <c r="P91">
-        <v>-57.316336945</v>
+        <v>-58.27556545</v>
       </c>
       <c r="Q91">
-        <v>-43.916336945</v>
+        <v>-44.87556545</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>1.081624386579583</v>
+        <v>1.185206825237541</v>
       </c>
       <c r="T91">
-        <v>7.222226032334878</v>
+        <v>7.944448635568367</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.0739402148998406</v>
+        <v>0.07311865695650903</v>
       </c>
       <c r="W91">
-        <v>0.2183648973266176</v>
+        <v>0.2185586206896552</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3286231773326248</v>
+        <v>0.3249718086955957</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.3152234411444438</v>
+        <v>0.3171234411444438</v>
       </c>
       <c r="C92">
-        <v>-173.7367526008688</v>
+        <v>-180.572379868467</v>
       </c>
       <c r="D92">
-        <v>226.5732473991312</v>
+        <v>224.986620131533</v>
       </c>
       <c r="E92">
-        <v>224.21</v>
+        <v>229.459</v>
       </c>
       <c r="F92">
-        <v>472.41</v>
+        <v>477.659</v>
       </c>
       <c r="G92">
         <v>72.09999999999999</v>
@@ -8825,37 +8825,37 @@
         <v>36.2</v>
       </c>
       <c r="M92">
-        <v>111.394278</v>
+        <v>112.6319922</v>
       </c>
       <c r="N92">
-        <v>-75.194278</v>
+        <v>-76.4319922</v>
       </c>
       <c r="O92">
-        <v>-16.91871255</v>
+        <v>-17.197198245</v>
       </c>
       <c r="P92">
-        <v>-58.27556545</v>
+        <v>-59.234793955</v>
       </c>
       <c r="Q92">
-        <v>-44.87556545</v>
+        <v>-45.834793955</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>1.185206825237541</v>
+        <v>1.311807583597268</v>
       </c>
       <c r="T92">
-        <v>7.944448635568367</v>
+        <v>8.827165150631521</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.07311865695650903</v>
+        <v>0.07231515523171222</v>
       </c>
       <c r="W92">
-        <v>0.2185586206896552</v>
+        <v>0.2187480863963623</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3249718086955957</v>
+        <v>0.3214006899187211</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.3171234411444438</v>
+        <v>0.3190234411444438</v>
       </c>
       <c r="C93">
-        <v>-180.572379868467</v>
+        <v>-187.385940275361</v>
       </c>
       <c r="D93">
-        <v>224.986620131533</v>
+        <v>223.4220597246391</v>
       </c>
       <c r="E93">
-        <v>229.459</v>
+        <v>234.708</v>
       </c>
       <c r="F93">
-        <v>477.659</v>
+        <v>482.908</v>
       </c>
       <c r="G93">
         <v>72.09999999999999</v>
@@ -8907,37 +8907,37 @@
         <v>36.2</v>
       </c>
       <c r="M93">
-        <v>112.6319922</v>
+        <v>113.8697064</v>
       </c>
       <c r="N93">
-        <v>-76.4319922</v>
+        <v>-77.66970640000001</v>
       </c>
       <c r="O93">
-        <v>-17.197198245</v>
+        <v>-17.47568394</v>
       </c>
       <c r="P93">
-        <v>-59.234793955</v>
+        <v>-60.19402246000001</v>
       </c>
       <c r="Q93">
-        <v>-45.834793955</v>
+        <v>-46.79402246000001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>1.311807583597268</v>
+        <v>1.470058531546927</v>
       </c>
       <c r="T93">
-        <v>8.827165150631521</v>
+        <v>9.930560794460462</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.07231515523171222</v>
+        <v>0.07152912093571534</v>
       </c>
       <c r="W93">
-        <v>0.2187480863963623</v>
+        <v>0.2189334332833583</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3214006899187211</v>
+        <v>0.3179072041587349</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.3190234411444438</v>
+        <v>0.3209234411444438</v>
       </c>
       <c r="C94">
-        <v>-187.385940275361</v>
+        <v>-194.1778910021729</v>
       </c>
       <c r="D94">
-        <v>223.4220597246391</v>
+        <v>221.8791089978271</v>
       </c>
       <c r="E94">
-        <v>234.708</v>
+        <v>239.957</v>
       </c>
       <c r="F94">
-        <v>482.908</v>
+        <v>488.157</v>
       </c>
       <c r="G94">
         <v>72.09999999999999</v>
@@ -8989,37 +8989,37 @@
         <v>36.2</v>
       </c>
       <c r="M94">
-        <v>113.8697064</v>
+        <v>115.1074206</v>
       </c>
       <c r="N94">
-        <v>-77.66970640000001</v>
+        <v>-78.90742059999999</v>
       </c>
       <c r="O94">
-        <v>-17.47568394</v>
+        <v>-17.754169635</v>
       </c>
       <c r="P94">
-        <v>-60.19402246000001</v>
+        <v>-61.153250965</v>
       </c>
       <c r="Q94">
-        <v>-46.79402246000001</v>
+        <v>-47.753250965</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.470058531546927</v>
+        <v>1.673524036053631</v>
       </c>
       <c r="T94">
-        <v>9.930560794460462</v>
+        <v>11.34921233652624</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.07152912093571534</v>
+        <v>0.07075999060307327</v>
       </c>
       <c r="W94">
-        <v>0.2189334332833583</v>
+        <v>0.2191147942157953</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3179072041587349</v>
+        <v>0.31448884712477</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.3209234411444438</v>
+        <v>0.3228234411444438</v>
       </c>
       <c r="C95">
-        <v>-194.1778910021729</v>
+        <v>-200.9486766870025</v>
       </c>
       <c r="D95">
-        <v>221.8791089978271</v>
+        <v>220.3573233129975</v>
       </c>
       <c r="E95">
-        <v>239.957</v>
+        <v>245.206</v>
       </c>
       <c r="F95">
-        <v>488.157</v>
+        <v>493.406</v>
       </c>
       <c r="G95">
         <v>72.09999999999999</v>
@@ -9071,37 +9071,37 @@
         <v>36.2</v>
       </c>
       <c r="M95">
-        <v>115.1074206</v>
+        <v>116.3451348</v>
       </c>
       <c r="N95">
-        <v>-78.90742059999999</v>
+        <v>-80.14513480000001</v>
       </c>
       <c r="O95">
-        <v>-17.754169635</v>
+        <v>-18.03265533</v>
       </c>
       <c r="P95">
-        <v>-61.153250965</v>
+        <v>-62.11247947000001</v>
       </c>
       <c r="Q95">
-        <v>-47.753250965</v>
+        <v>-48.71247947000001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.673524036053631</v>
+        <v>1.944811375395903</v>
       </c>
       <c r="T95">
-        <v>11.34921233652624</v>
+        <v>13.24074772594729</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.07075999060307327</v>
+        <v>0.07000722474559375</v>
       </c>
       <c r="W95">
-        <v>0.2191147942157953</v>
+        <v>0.219292296404989</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.31448884712477</v>
+        <v>0.3111432210915277</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.3228234411444438</v>
+        <v>0.3247234411444437</v>
       </c>
       <c r="C96">
-        <v>-200.9486766870025</v>
+        <v>-207.6987298526197</v>
       </c>
       <c r="D96">
-        <v>220.3573233129975</v>
+        <v>218.8562701473803</v>
       </c>
       <c r="E96">
-        <v>245.206</v>
+        <v>250.455</v>
       </c>
       <c r="F96">
-        <v>493.406</v>
+        <v>498.655</v>
       </c>
       <c r="G96">
         <v>72.09999999999999</v>
@@ -9153,37 +9153,37 @@
         <v>36.2</v>
       </c>
       <c r="M96">
-        <v>116.3451348</v>
+        <v>117.582849</v>
       </c>
       <c r="N96">
-        <v>-80.14513480000001</v>
+        <v>-81.38284900000001</v>
       </c>
       <c r="O96">
-        <v>-18.03265533</v>
+        <v>-18.311141025</v>
       </c>
       <c r="P96">
-        <v>-62.11247947000001</v>
+        <v>-63.07170797500001</v>
       </c>
       <c r="Q96">
-        <v>-48.71247947000001</v>
+        <v>-49.67170797500001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.944811375395903</v>
+        <v>2.324613650475085</v>
       </c>
       <c r="T96">
-        <v>13.24074772594729</v>
+        <v>15.88889727113676</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.07000722474559375</v>
+        <v>0.06927030659037696</v>
       </c>
       <c r="W96">
-        <v>0.219292296404989</v>
+        <v>0.2194660617059891</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3111432210915277</v>
+        <v>0.3078680292905643</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.3247234411444437</v>
+        <v>0.3266234411444437</v>
       </c>
       <c r="C97">
-        <v>-207.6987298526197</v>
+        <v>-214.4284713163144</v>
       </c>
       <c r="D97">
-        <v>218.8562701473803</v>
+        <v>217.3755286836856</v>
       </c>
       <c r="E97">
-        <v>250.455</v>
+        <v>255.704</v>
       </c>
       <c r="F97">
-        <v>498.655</v>
+        <v>503.904</v>
       </c>
       <c r="G97">
         <v>72.09999999999999</v>
@@ -9235,37 +9235,37 @@
         <v>36.2</v>
       </c>
       <c r="M97">
-        <v>117.582849</v>
+        <v>118.8205632</v>
       </c>
       <c r="N97">
-        <v>-81.38284900000001</v>
+        <v>-82.62056320000001</v>
       </c>
       <c r="O97">
-        <v>-18.311141025</v>
+        <v>-18.58962672</v>
       </c>
       <c r="P97">
-        <v>-63.07170797500001</v>
+        <v>-64.03093648000001</v>
       </c>
       <c r="Q97">
-        <v>-49.67170797500001</v>
+        <v>-50.63093648000001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>2.324613650475085</v>
+        <v>2.894317063093858</v>
       </c>
       <c r="T97">
-        <v>15.88889727113676</v>
+        <v>19.86112158892095</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.06927030659037696</v>
+        <v>0.06854874089672722</v>
       </c>
       <c r="W97">
-        <v>0.2194660617059891</v>
+        <v>0.2196362068965517</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3078680292905643</v>
+        <v>0.3046610706521209</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.3266234411444437</v>
+        <v>0.3285234411444438</v>
       </c>
       <c r="C98">
-        <v>-214.4284713163144</v>
+        <v>-221.1383105832219</v>
       </c>
       <c r="D98">
-        <v>217.3755286836856</v>
+        <v>215.9146894167781</v>
       </c>
       <c r="E98">
-        <v>255.704</v>
+        <v>260.953</v>
       </c>
       <c r="F98">
-        <v>503.9039999999999</v>
+        <v>509.153</v>
       </c>
       <c r="G98">
         <v>72.09999999999999</v>
@@ -9317,37 +9317,37 @@
         <v>36.2</v>
       </c>
       <c r="M98">
-        <v>118.8205632</v>
+        <v>120.0582774</v>
       </c>
       <c r="N98">
-        <v>-82.62056319999999</v>
+        <v>-83.85827739999999</v>
       </c>
       <c r="O98">
-        <v>-18.58962672</v>
+        <v>-18.868112415</v>
       </c>
       <c r="P98">
-        <v>-64.03093647999999</v>
+        <v>-64.99016498499999</v>
       </c>
       <c r="Q98">
-        <v>-50.63093648</v>
+        <v>-51.59016498499999</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>2.89431706309385</v>
+        <v>3.843822750791801</v>
       </c>
       <c r="T98">
-        <v>19.8611215889209</v>
+        <v>26.48149545189453</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.06854874089672722</v>
+        <v>0.06784205284624549</v>
       </c>
       <c r="W98">
-        <v>0.2196362068965517</v>
+        <v>0.2198028439388553</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.304661070652121</v>
+        <v>0.3015202348722021</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.3285234411444438</v>
+        <v>0.3304234411444438</v>
       </c>
       <c r="C99">
-        <v>-221.1383105832219</v>
+        <v>-227.8286462238927</v>
       </c>
       <c r="D99">
-        <v>215.9146894167781</v>
+        <v>214.4733537761072</v>
       </c>
       <c r="E99">
-        <v>260.953</v>
+        <v>266.2019999999999</v>
       </c>
       <c r="F99">
-        <v>509.153</v>
+        <v>514.4019999999999</v>
       </c>
       <c r="G99">
         <v>72.09999999999999</v>
@@ -9399,37 +9399,37 @@
         <v>36.2</v>
       </c>
       <c r="M99">
-        <v>120.0582774</v>
+        <v>121.2959916</v>
       </c>
       <c r="N99">
-        <v>-83.85827739999999</v>
+        <v>-85.09599159999999</v>
       </c>
       <c r="O99">
-        <v>-18.868112415</v>
+        <v>-19.14659811</v>
       </c>
       <c r="P99">
-        <v>-64.99016498499999</v>
+        <v>-65.94939348999999</v>
       </c>
       <c r="Q99">
-        <v>-51.59016498499999</v>
+        <v>-52.54939348999999</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>3.843822750791801</v>
+        <v>5.7428341261877</v>
       </c>
       <c r="T99">
-        <v>26.48149545189453</v>
+        <v>39.7222431778418</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.06784205284624549</v>
+        <v>0.06714978700087564</v>
       </c>
       <c r="W99">
-        <v>0.2198028439388553</v>
+        <v>0.2199660802251935</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3015202348722021</v>
+        <v>0.2984434977816696</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.3304234411444438</v>
+        <v>0.3323234411444438</v>
       </c>
       <c r="C100">
-        <v>-227.8286462238927</v>
+        <v>-234.4998662368416</v>
       </c>
       <c r="D100">
-        <v>214.4733537761072</v>
+        <v>213.0511337631584</v>
       </c>
       <c r="E100">
-        <v>266.2019999999999</v>
+        <v>271.451</v>
       </c>
       <c r="F100">
-        <v>514.4019999999999</v>
+        <v>519.651</v>
       </c>
       <c r="G100">
         <v>72.09999999999999</v>
@@ -9481,37 +9481,37 @@
         <v>36.2</v>
       </c>
       <c r="M100">
-        <v>121.2959916</v>
+        <v>122.5337058</v>
       </c>
       <c r="N100">
-        <v>-85.09599159999999</v>
+        <v>-86.33370579999999</v>
       </c>
       <c r="O100">
-        <v>-19.14659811</v>
+        <v>-19.425083805</v>
       </c>
       <c r="P100">
-        <v>-65.94939348999999</v>
+        <v>-66.90862199499999</v>
       </c>
       <c r="Q100">
-        <v>-52.54939348999999</v>
+        <v>-53.50862199499999</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>5.7428341261877</v>
+        <v>11.4398682523754</v>
       </c>
       <c r="T100">
-        <v>39.7222431778418</v>
+        <v>79.44448635568359</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.06714978700087564</v>
+        <v>0.06647150632409912</v>
       </c>
       <c r="W100">
-        <v>0.2199660802251935</v>
+        <v>0.2201260188087774</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2984434977816696</v>
+        <v>0.295428916995996</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.3323234411444438</v>
-      </c>
-      <c r="C101">
-        <v>-234.4998662368416</v>
-      </c>
-      <c r="D101">
-        <v>213.0511337631584</v>
-      </c>
-      <c r="E101">
-        <v>271.451</v>
-      </c>
-      <c r="F101">
-        <v>519.651</v>
-      </c>
-      <c r="G101">
-        <v>72.09999999999999</v>
-      </c>
-      <c r="H101">
-        <v>276.7</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>49.6</v>
-      </c>
-      <c r="K101">
-        <v>13.4</v>
-      </c>
-      <c r="L101">
-        <v>36.2</v>
-      </c>
-      <c r="M101">
-        <v>122.5337058</v>
-      </c>
-      <c r="N101">
-        <v>-86.33370579999999</v>
-      </c>
-      <c r="O101">
-        <v>-19.425083805</v>
-      </c>
-      <c r="P101">
-        <v>-66.90862199499999</v>
-      </c>
-      <c r="Q101">
-        <v>-53.50862199499999</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>11.4398682523754</v>
-      </c>
-      <c r="T101">
-        <v>79.44448635568359</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.06647150632409912</v>
-      </c>
-      <c r="W101">
-        <v>0.2201260188087774</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.295428916995996</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
